--- a/LCA/eco-optimization_tool/Appendix/Inventory/Inventaire ACV.xlsx
+++ b/LCA/eco-optimization_tool/Appendix/Inventory/Inventaire ACV.xlsx
@@ -1,16 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\prevosad\Documents\Recherche\Projets\ACV\Acv_eol\code\sustain-4-SWT\LCA\eco-optimization_tool\Appendix\Inventory\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FC5AACC-8E07-4BE3-808F-07EDE547B66B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Wing generator" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="Structure" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="Electronics" sheetId="3" r:id="rId6"/>
-    <sheet state="visible" name="Hardware structure" sheetId="4" r:id="rId7"/>
-    <sheet state="visible" name="Hardware gene" sheetId="5" r:id="rId8"/>
+    <sheet name="Wind generator" sheetId="1" r:id="rId1"/>
+    <sheet name="Structure" sheetId="2" r:id="rId2"/>
+    <sheet name="Electronics" sheetId="3" r:id="rId3"/>
+    <sheet name="Hardware structure" sheetId="4" r:id="rId4"/>
+    <sheet name="Hardware gene" sheetId="5" r:id="rId5"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataChecksum="ciqt4JKNnh4DbcccZk2dFetehnxHTEBI0YTY15739QU="/>
@@ -20,23 +29,31 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment authorId="0" ref="M21">
+    <comment ref="N21" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
-        <t xml:space="preserve">======
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>======
 ID#AAABpywjpOQ
     (2025-08-25 15:22:25)
 pieces partout car coils c'est pour des plaques(faux ami)
 	-La Raphinerie</t>
+        </r>
       </text>
     </comment>
   </commentList>
   <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
+    <ext xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mjJrRcpDD1YUc0Wah90ayIYn19iUg=="/>
     </ext>
   </extLst>
@@ -44,32 +61,123 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment authorId="0" ref="D1">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
       <text>
-        <t xml:space="preserve">======
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>======
+ID#AAABpywjpN0
+    (2025-08-25 15:22:25)
+https://www.chausson.fr/quincaillerie/cheville-frapper-long-xtrem-spit-avec-vis-tete-fraisee-zinguee-10x160mm-boite-50-p-47707-1
+	-La Raphinerie</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>======
 ID#AAABpywjpOw
     (2025-08-25 15:22:25)
 https://www.boltport.com/weights/din-934/
 	-La Raphinerie</t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="H1">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000006000000}">
       <text>
-        <t xml:space="preserve">======
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>======
+ID#AAABpywjpNk
+    (2025-08-25 15:22:25)
+https://www.simafrance.com/fr/tendeurs/117-tendeur-standard-chape-chape-.html
+	-La Raphinerie</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000005000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>======
+ID#AAABpywjpNo
+    (2025-08-25 15:22:25)
+https://www.prolev.fr/dynamic/pdf/fiches/manille_lyre_haute_resistance_hr_fiche_technique_prolev_3.pdf
+	-La Raphinerie</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000007000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>======
+ID#AAABpytb5Og
+    (2025-08-25 15:22:25)
+https://www.greenpin.com/sites/default/files/2021-06/DO_FR_CATFR_Catalogue_3.%20Wire%20Rope%20Clips.pdf
+	-La Raphinerie</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>======
 ID#AAABpywjpOI
     (2025-08-25 15:22:25)
 https://www.dispano.fr/p/outillage-quincaillerie/cosse-coeur-standard-pour-cable-diametre-6mm-en-acier-zingue-blanc-ccl106-A1474858
 	-La Raphinerie</t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="J1">
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
       <text>
-        <t xml:space="preserve">======
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>======
 ID#AAABpywjpOE
     (2025-08-25 15:22:25)
 Ajouter ref
@@ -77,47 +185,12 @@
 90m²/t : https://www.researchgate.net/publication/278314426_Handbook_of_Hot-Dip_Galvanization
 60 m²/t : https://ecoquery.ecoinvent.org/3.11/cutoff/dataset/7951/documentation
 	-La Raphinerie</t>
-      </text>
-    </comment>
-    <comment authorId="0" ref="C1">
-      <text>
-        <t xml:space="preserve">======
-ID#AAABpywjpN0
-    (2025-08-25 15:22:25)
-https://www.chausson.fr/quincaillerie/cheville-frapper-long-xtrem-spit-avec-vis-tete-fraisee-zinguee-10x160mm-boite-50-p-47707-1
-	-La Raphinerie</t>
-      </text>
-    </comment>
-    <comment authorId="0" ref="F1">
-      <text>
-        <t xml:space="preserve">======
-ID#AAABpywjpNo
-    (2025-08-25 15:22:25)
-https://www.prolev.fr/dynamic/pdf/fiches/manille_lyre_haute_resistance_hr_fiche_technique_prolev_3.pdf
-	-La Raphinerie</t>
-      </text>
-    </comment>
-    <comment authorId="0" ref="E1">
-      <text>
-        <t xml:space="preserve">======
-ID#AAABpywjpNk
-    (2025-08-25 15:22:25)
-https://www.simafrance.com/fr/tendeurs/117-tendeur-standard-chape-chape-.html
-	-La Raphinerie</t>
-      </text>
-    </comment>
-    <comment authorId="0" ref="G1">
-      <text>
-        <t xml:space="preserve">======
-ID#AAABpytb5Og
-    (2025-08-25 15:22:25)
-https://www.greenpin.com/sites/default/files/2021-06/DO_FR_CATFR_Catalogue_3.%20Wire%20Rope%20Clips.pdf
-	-La Raphinerie</t>
+        </r>
       </text>
     </comment>
   </commentList>
   <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
+    <ext xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mj106/WeV/qrD1xeQahVIHAVXuKqQ=="/>
     </ext>
   </extLst>
@@ -125,59 +198,99 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment authorId="0" ref="A5">
+    <comment ref="A5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000001000000}">
       <text>
-        <t xml:space="preserve">======
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>======
 ID#AAABpywjpOk
     (2025-08-25 15:22:25)
 https://www.boltport.com/weights/din-934/
 	-La Raphinerie</t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="A9">
+    <comment ref="A7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000004000000}">
       <text>
-        <t xml:space="preserve">======
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>======
+ID#AAABpywjpOA
+    (2025-08-25 15:22:25)
+https://www.gbm-france.com/boutique/connectique-de-terre/boulonnerie-inox/rondelles-plates-en-inox/rondelle-plate-m12-en-inox/
+	-La Raphinerie</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000002000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>======
 ID#AAABpywjpOU
     (2025-08-25 15:22:25)
 https://www.acton.fr/index.php?ent_id=1&amp;cat_id=2&amp;ni1_id=30&amp;ni2_id=47&amp;ni3_id=71&amp;ni4_id=317&amp;csaction=site%2Fentite%2Fcatalogue%2Fdetail_technique_filtrer&amp;ent_id=1&amp;cat_id=2&amp;ni1_id=30&amp;ni2_id=47&amp;ni3_id=71&amp;ni4_id=317&amp;colonne=9&amp;filtre=5X40&amp;%23=breadcrumb
 	-La Raphinerie</t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="A20">
+    <comment ref="A18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000005000000}">
       <text>
-        <t xml:space="preserve">======
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>======
+ID#AAABpywjpNs
+    (2025-08-25 15:22:25)
+https://www.chausson.fr/quincaillerie/vis-bois-rocket-tete-fraisee-torx-acier-zingue-filetage-total-5x50mm-p-685107-1
+	-La Raphinerie</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000003000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>======
 ID#AAABpywjpOM
     (2025-08-25 15:22:25)
 https://www.vis-express.fr/vba-vis-bois-agglo-tete-fraisee-tf-torx-filetage-partiel-inox-a2-doc-8231/35025-vba-vis-bois-agglo-inox-a2-tete-fraisee-tf-5x30-filetee-sur-18-torx-t25.html
 	-La Raphinerie</t>
-      </text>
-    </comment>
-    <comment authorId="0" ref="A7">
-      <text>
-        <t xml:space="preserve">======
-ID#AAABpywjpOA
-    (2025-08-25 15:22:25)
-https://www.gbm-france.com/boutique/connectique-de-terre/boulonnerie-inox/rondelles-plates-en-inox/rondelle-plate-m12-en-inox/
-	-La Raphinerie</t>
-      </text>
-    </comment>
-    <comment authorId="0" ref="A18">
-      <text>
-        <t xml:space="preserve">======
-ID#AAABpywjpNs
-    (2025-08-25 15:22:25)
-https://www.chausson.fr/quincaillerie/vis-bois-rocket-tete-fraisee-torx-acier-zingue-filetage-total-5x50mm-p-685107-1
-	-La Raphinerie</t>
+        </r>
       </text>
     </comment>
   </commentList>
   <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
+    <ext xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mheRzaQheqAxzoFKtfM0hXD5KLimw=="/>
     </ext>
   </extLst>
@@ -185,7 +298,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="374">
   <si>
     <t>Sub-system</t>
   </si>
@@ -260,12 +373,6 @@
   </si>
   <si>
     <t>Copper recovery is sometimes accepted by metal recyclers, although not always. At end of life, the resin can be burned or melted, allowing copper to be recovered. Without protective paint, the resin degrades under UV exposure and rain, leaving the fiberglass exposed—resulting in a lifespan of around 5 years. If protected, the coating should be renewed every 5 to 10 years, enabling a service life of 20 years or more. Main failure risks include short circuits, impacts, or excessive friction. In most cases, the stator is not recovered, as it tends to break more easily than other components.</t>
-  </si>
-  <si>
-    <t>Sheet rolling</t>
-  </si>
-  <si>
-    <t>sheet rolling, copper-RER</t>
   </si>
   <si>
     <t>Wire drawing</t>
@@ -1327,98 +1434,108 @@
   <si>
     <t>Poids zinc [kg]</t>
   </si>
+  <si>
+    <t>Reference in the manual</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="17">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
-    <font/>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="8.0"/>
+      <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="8.0"/>
+      <sz val="8"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="8.0"/>
+      <sz val="8"/>
       <color theme="1"/>
       <name val="&quot;Liberation Sans&quot;"/>
     </font>
     <font>
       <b/>
-      <sz val="8.0"/>
+      <sz val="8"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="8.0"/>
+      <sz val="8"/>
       <color theme="1"/>
       <name val="&quot;Liberation Sans&quot;"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="&quot;Liberation Sans&quot;"/>
     </font>
@@ -1428,7 +1545,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1534,11 +1651,21 @@
     </fill>
   </fills>
   <borders count="9">
-    <border/>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1547,11 +1674,18 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1563,6 +1697,8 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1571,14 +1707,20 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1593,306 +1735,1277 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="98">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="8" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="8" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="8" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="10" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="11" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="11" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="12" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="12" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="164" fontId="4" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="12" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="164" fontId="4" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="12" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="9" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="10" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="164" fontId="4" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="11" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="2" fontId="4" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="11" fontId="4" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="165" fontId="4" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="11" fontId="4" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="13" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="12" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="13" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="12" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="12" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="164" fontId="4" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="11" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="11" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="12" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="2" fillId="12" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="164" fontId="4" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="11" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="11" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="11" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="11" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="12" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="12" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="11" fontId="4" numFmtId="11" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="11" fontId="4" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="9" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="13" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="11" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="11" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="14" fontId="8" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="2" fillId="15" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf borderId="2" fillId="16" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf borderId="2" fillId="16" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="14" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="2" fillId="17" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf borderId="2" fillId="18" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf borderId="2" fillId="18" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf borderId="2" fillId="17" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf borderId="2" fillId="16" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf borderId="2" fillId="18" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="15" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf borderId="5" fillId="17" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf borderId="5" fillId="18" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf borderId="5" fillId="18" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="13" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="14" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="14" numFmtId="2" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf borderId="7" fillId="0" fontId="15" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="16" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="2" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="2" fillId="0" fontId="4" numFmtId="2" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="0" fontId="4" numFmtId="2" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="fr-FR"/>
+              <a:t>Zinc</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="fr-FR" baseline="0"/>
+              <a:t> coating area in function of tower height</a:t>
+            </a:r>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="fr-FR"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Hardware structure'!$A$2:$A$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>24</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Hardware structure'!$J$2:$J$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.73162800000000006</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.086144</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.3939440000000003</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0870-49B0-BE6A-54089AD35111}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="707487647"/>
+        <c:axId val="701120015"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="707487647"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="701120015"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="701120015"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="707487647"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>685800</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Graphique 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A16727C6-9FF5-4423-A851-8134ED8C6B0B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -2082,25 +3195,28 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <dimension ref="A1:H997"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10.75"/>
-    <col customWidth="1" min="2" max="5" width="12.63"/>
-    <col customWidth="1" min="6" max="6" width="24.75"/>
-    <col customWidth="1" min="7" max="7" width="46.5"/>
-    <col customWidth="1" min="8" max="8" width="19.25"/>
+    <col min="1" max="1" width="10.77734375" customWidth="1"/>
+    <col min="2" max="5" width="12.6640625" customWidth="1"/>
+    <col min="6" max="6" width="24.77734375" customWidth="1"/>
+    <col min="7" max="7" width="46.44140625" customWidth="1"/>
+    <col min="8" max="8" width="19.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1" spans="1:8" ht="15.75" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -2124,7 +3240,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
+    <row r="2" spans="1:8" ht="15.75" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
@@ -2148,7 +3264,7 @@
       </c>
       <c r="H2" s="5"/>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1">
       <c r="A3" s="3"/>
       <c r="B3" s="4"/>
       <c r="C3" s="7" t="s">
@@ -2168,7 +3284,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" ht="39.0" customHeight="1">
+    <row r="4" spans="1:8" ht="39" customHeight="1">
       <c r="A4" s="8"/>
       <c r="B4" s="9" t="s">
         <v>19</v>
@@ -2185,12 +3301,12 @@
       <c r="F4" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="93" t="s">
         <v>24</v>
       </c>
       <c r="H4" s="5"/>
     </row>
-    <row r="5" ht="42.75" customHeight="1">
+    <row r="5" spans="1:8" ht="44.25" customHeight="1">
       <c r="A5" s="8"/>
       <c r="B5" s="9"/>
       <c r="C5" s="5"/>
@@ -2201,32 +3317,32 @@
       <c r="F5" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="10"/>
+      <c r="G5" s="94"/>
       <c r="H5" s="5"/>
     </row>
-    <row r="6" ht="44.25" customHeight="1">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1">
       <c r="A6" s="8"/>
       <c r="B6" s="9"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5" t="s">
+      <c r="C6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="D6" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="5"/>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
+      <c r="E6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" customHeight="1">
       <c r="A7" s="8"/>
       <c r="B7" s="9"/>
-      <c r="C7" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>30</v>
-      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
       <c r="E7" s="7" t="s">
         <v>31</v>
       </c>
@@ -2236,7 +3352,7 @@
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
+    <row r="8" spans="1:8" ht="15.75" customHeight="1">
       <c r="A8" s="8"/>
       <c r="B8" s="9"/>
       <c r="C8" s="7"/>
@@ -2250,39 +3366,39 @@
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
     </row>
-    <row r="9" ht="15.75" customHeight="1">
+    <row r="9" spans="1:8" ht="15.75" customHeight="1">
       <c r="A9" s="8"/>
       <c r="B9" s="9"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7" t="s">
+      <c r="C9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="E9" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-    </row>
-    <row r="10" ht="15.75" customHeight="1">
+      <c r="F9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="5"/>
+      <c r="H9" s="11"/>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" customHeight="1">
       <c r="A10" s="8"/>
       <c r="B10" s="9"/>
-      <c r="C10" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" s="11" t="s">
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5" t="s">
         <v>38</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>39</v>
       </c>
       <c r="G10" s="5"/>
-      <c r="H10" s="12"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1">
+      <c r="H10" s="11"/>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" customHeight="1">
       <c r="A11" s="8"/>
       <c r="B11" s="9"/>
       <c r="C11" s="5"/>
@@ -2294,85 +3410,85 @@
         <v>41</v>
       </c>
       <c r="G11" s="5"/>
-      <c r="H11" s="12"/>
-    </row>
-    <row r="12" ht="15.75" customHeight="1">
+      <c r="H11" s="11"/>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" customHeight="1">
       <c r="A12" s="8"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5" t="s">
+      <c r="B12" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="C12" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G12" s="5"/>
-      <c r="H12" s="12"/>
-    </row>
-    <row r="13" ht="15.75" customHeight="1">
+      <c r="D12" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H12" s="7"/>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" customHeight="1">
       <c r="A13" s="8"/>
-      <c r="B13" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>46</v>
-      </c>
+      <c r="B13" s="12"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
       <c r="E13" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="G13" s="7" t="s">
         <v>49</v>
       </c>
+      <c r="G13" s="7"/>
       <c r="H13" s="7"/>
     </row>
-    <row r="14" ht="15.75" customHeight="1">
+    <row r="14" spans="1:8" ht="39.75" customHeight="1">
       <c r="A14" s="8"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7" t="s">
+      <c r="B14" s="12"/>
+      <c r="C14" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="D14" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-    </row>
-    <row r="15" ht="39.75" customHeight="1">
+      <c r="E14" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="G14" s="13"/>
+      <c r="H14" s="14"/>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" customHeight="1">
       <c r="A15" s="8"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="F15" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="G15" s="14"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G15" s="7"/>
       <c r="H15" s="15"/>
     </row>
-    <row r="16" ht="15.75" customHeight="1">
+    <row r="16" spans="1:8" ht="15.75" customHeight="1">
       <c r="A16" s="8"/>
-      <c r="B16" s="13"/>
-      <c r="C16" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>37</v>
-      </c>
+      <c r="B16" s="12"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
       <c r="E16" s="7" t="s">
         <v>38</v>
       </c>
@@ -2380,11 +3496,11 @@
         <v>39</v>
       </c>
       <c r="G16" s="7"/>
-      <c r="H16" s="16"/>
-    </row>
-    <row r="17" ht="15.75" customHeight="1">
+      <c r="H16" s="15"/>
+    </row>
+    <row r="17" spans="1:8" ht="15.75" customHeight="1">
       <c r="A17" s="8"/>
-      <c r="B17" s="13"/>
+      <c r="B17" s="12"/>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
       <c r="E17" s="7" t="s">
@@ -2394,414 +3510,401 @@
         <v>41</v>
       </c>
       <c r="G17" s="7"/>
-      <c r="H17" s="16"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1">
+      <c r="H17" s="15"/>
+    </row>
+    <row r="18" spans="1:8" ht="55.5" customHeight="1">
       <c r="A18" s="8"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="G18" s="7"/>
-      <c r="H18" s="16"/>
-    </row>
-    <row r="19" ht="55.5" customHeight="1">
+      <c r="B18" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H18" s="13"/>
+    </row>
+    <row r="19" spans="1:8" ht="15.75" customHeight="1">
       <c r="A19" s="8"/>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14" t="s">
+      <c r="C19" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="H19" s="14"/>
-    </row>
-    <row r="20" ht="15.75" customHeight="1">
+      <c r="D19" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="H19" s="13"/>
+    </row>
+    <row r="20" spans="1:8" ht="15.75" customHeight="1">
       <c r="A20" s="8"/>
-      <c r="B20" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="C20" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D20" s="14" t="s">
+      <c r="B20" s="12"/>
+      <c r="C20" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="E20" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="F20" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="G20" s="14" t="s">
+      <c r="D20" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="H20" s="14"/>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
+      <c r="E20" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="H20" s="13"/>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" customHeight="1">
       <c r="A21" s="8"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="E21" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="F21" s="14" t="s">
+      <c r="B21" s="12"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="G21" s="14" t="s">
+      <c r="F21" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="H21" s="14"/>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+    </row>
+    <row r="22" spans="1:8" ht="15.75" customHeight="1">
       <c r="A22" s="8"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14" t="s">
+      <c r="B22" s="12"/>
+      <c r="C22" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="F22" s="14" t="s">
+      <c r="D22" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
+      <c r="E22" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+    </row>
+    <row r="23" spans="1:8" ht="15.75" customHeight="1">
       <c r="A23" s="8"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="14" t="s">
+      <c r="B23" s="12"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+    </row>
+    <row r="24" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A24" s="8"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F24" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="D23" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="F23" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="8"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="F24" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+    </row>
+    <row r="25" spans="1:8" ht="15.75" customHeight="1">
       <c r="A25" s="8"/>
-      <c r="B25" s="13"/>
-      <c r="C25" s="14" t="s">
+      <c r="B25" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D25" s="14" t="s">
+      <c r="C25" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="E25" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="F25" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
+      <c r="D25" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F25" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="H25" s="13"/>
+    </row>
+    <row r="26" spans="1:8" ht="15.75" customHeight="1">
       <c r="A26" s="8"/>
-      <c r="B26" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="D26" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="E26" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="F26" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="G26" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="H26" s="14"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
+      <c r="B26" s="9"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="F26" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+    </row>
+    <row r="27" spans="1:8" ht="15.75" customHeight="1">
       <c r="A27" s="8"/>
       <c r="B27" s="9"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="F27" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
+      <c r="C27" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+    </row>
+    <row r="28" spans="1:8" ht="15.75" customHeight="1">
       <c r="A28" s="8"/>
       <c r="B28" s="9"/>
-      <c r="C28" s="14" t="s">
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+    </row>
+    <row r="29" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A29" s="8"/>
+      <c r="B29" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="D28" s="14" t="s">
+      <c r="C29" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="E28" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="F28" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="8"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
+      <c r="D29" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>82</v>
+      </c>
       <c r="H29" s="14"/>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
+    <row r="30" spans="1:8" ht="15.75" customHeight="1">
       <c r="A30" s="8"/>
-      <c r="B30" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="C30" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="D30" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="E30" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="F30" s="14" t="s">
+      <c r="B30" s="12"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="G30" s="14" t="s">
+      <c r="F30" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="H30" s="15"/>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
+      <c r="G30" s="13"/>
+      <c r="H30" s="14"/>
+    </row>
+    <row r="31" spans="1:8" ht="15.75" customHeight="1">
       <c r="A31" s="8"/>
-      <c r="B31" s="13"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14" t="s">
+      <c r="B31" s="12"/>
+      <c r="C31" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="F31" s="14" t="s">
+      <c r="D31" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="G31" s="14"/>
-      <c r="H31" s="15"/>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
+      <c r="E31" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="H31" s="14"/>
+    </row>
+    <row r="32" spans="1:8" ht="15.75" customHeight="1">
       <c r="A32" s="8"/>
-      <c r="B32" s="13"/>
-      <c r="C32" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="D32" s="14" t="s">
+      <c r="B32" s="12"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="F32" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="E32" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="F32" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="G32" s="14" t="s">
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+    </row>
+    <row r="33" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A33" s="8"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+    </row>
+    <row r="34" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A34" s="8"/>
+      <c r="B34" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="H32" s="15"/>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="8"/>
-      <c r="B33" s="13"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="F33" s="14" t="s">
+      <c r="C34" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="8"/>
-      <c r="B34" s="13"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="F34" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
+      <c r="D34" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="E34" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="H34" s="13"/>
+    </row>
+    <row r="35" spans="1:8" ht="15.75" customHeight="1">
       <c r="A35" s="8"/>
-      <c r="B35" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="C35" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="D35" s="14" t="s">
+      <c r="B35" s="9"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="E35" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="H35" s="14"/>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+    </row>
+    <row r="36" spans="1:8" ht="15.75" customHeight="1">
       <c r="A36" s="8"/>
       <c r="B36" s="9"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14" t="s">
+      <c r="C36" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D36" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
+      <c r="E36" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="H36" s="13"/>
+    </row>
+    <row r="37" spans="1:8" ht="15.75" customHeight="1">
       <c r="A37" s="8"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="D37" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="E37" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="H37" s="14"/>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="8"/>
-      <c r="B38" s="13"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="17"/>
-      <c r="B39" s="18"/>
-      <c r="C39" s="17"/>
-      <c r="D39" s="17"/>
-      <c r="E39" s="17"/>
-      <c r="F39" s="17"/>
-      <c r="G39" s="17"/>
-      <c r="H39" s="17"/>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="19"/>
-      <c r="B40" s="20"/>
-      <c r="C40" s="19"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19"/>
-      <c r="F40" s="19"/>
-      <c r="G40" s="19"/>
-      <c r="H40" s="19"/>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="19"/>
-      <c r="B41" s="20"/>
-      <c r="C41" s="19"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="19"/>
-      <c r="H41" s="19"/>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="19"/>
-      <c r="B42" s="20"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="19"/>
-      <c r="G42" s="19"/>
-      <c r="H42" s="19"/>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="19"/>
+      <c r="B37" s="12"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+    </row>
+    <row r="38" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A38" s="16"/>
+      <c r="B38" s="17"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="16"/>
+      <c r="H38" s="16"/>
+    </row>
+    <row r="39" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A39" s="18"/>
+      <c r="B39" s="19"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="18"/>
+      <c r="H39" s="18"/>
+    </row>
+    <row r="40" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A40" s="18"/>
+      <c r="B40" s="19"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
+    </row>
+    <row r="41" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A41" s="18"/>
+      <c r="B41" s="19"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
+    </row>
+    <row r="42" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A42" s="18"/>
+      <c r="B42" s="19"/>
+      <c r="C42" s="18"/>
+      <c r="D42" s="18"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="18"/>
+      <c r="H42" s="18"/>
+    </row>
+    <row r="43" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A43" s="18"/>
       <c r="B43" s="20"/>
-      <c r="C43" s="19"/>
-      <c r="D43" s="19"/>
-      <c r="E43" s="19"/>
-      <c r="F43" s="19"/>
-      <c r="G43" s="19"/>
-      <c r="H43" s="19"/>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="19"/>
-      <c r="B44" s="21"/>
-      <c r="C44" s="19"/>
-      <c r="D44" s="19"/>
-      <c r="E44" s="19"/>
-      <c r="F44" s="19"/>
-      <c r="G44" s="19"/>
-      <c r="H44" s="19"/>
-    </row>
-    <row r="45" ht="15.75" customHeight="1"/>
-    <row r="46" ht="15.75" customHeight="1"/>
-    <row r="47" ht="15.75" customHeight="1"/>
-    <row r="48" ht="15.75" customHeight="1"/>
+      <c r="C43" s="18"/>
+      <c r="D43" s="18"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="18"/>
+      <c r="H43" s="18"/>
+    </row>
+    <row r="44" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="45" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="46" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="47" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="48" spans="1:8" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>
@@ -3751,1101 +4854,1139 @@
     <row r="995" ht="15.75" customHeight="1"/>
     <row r="996" ht="15.75" customHeight="1"/>
     <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="G4:G6"/>
+    <mergeCell ref="G4:G5"/>
   </mergeCells>
-  <printOptions gridLines="1" horizontalCentered="1"/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.25" right="0.25" top="0.75"/>
-  <pageSetup paperSize="9" cellComments="atEnd" orientation="portrait" pageOrder="overThenDown"/>
-  <drawing r:id="rId1"/>
+  <printOptions horizontalCentered="1" gridLines="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="9" pageOrder="overThenDown" orientation="portrait" cellComments="atEnd"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <dimension ref="A1:N997"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10.13"/>
-    <col customWidth="1" min="2" max="2" width="15.25"/>
-    <col customWidth="1" min="3" max="3" width="8.88"/>
-    <col customWidth="1" min="4" max="4" width="10.13"/>
-    <col customWidth="1" min="5" max="5" width="15.25"/>
-    <col customWidth="1" min="6" max="6" width="29.25"/>
-    <col customWidth="1" min="7" max="7" width="33.38"/>
-    <col customWidth="1" min="8" max="8" width="17.75"/>
-    <col customWidth="1" min="9" max="9" width="21.13"/>
-    <col customWidth="1" min="10" max="10" width="24.88"/>
-    <col customWidth="1" min="13" max="13" width="21.0"/>
+    <col min="1" max="1" width="10.109375" customWidth="1"/>
+    <col min="2" max="2" width="15.21875" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" customWidth="1"/>
+    <col min="4" max="4" width="10.109375" customWidth="1"/>
+    <col min="5" max="5" width="15.21875" customWidth="1"/>
+    <col min="6" max="6" width="29.21875" customWidth="1"/>
+    <col min="7" max="7" width="33.33203125" customWidth="1"/>
+    <col min="8" max="8" width="28.21875" style="92" customWidth="1"/>
+    <col min="9" max="9" width="17.77734375" customWidth="1"/>
+    <col min="10" max="10" width="21.109375" customWidth="1"/>
+    <col min="11" max="11" width="24.88671875" customWidth="1"/>
+    <col min="14" max="14" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35.25" customHeight="1">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:14" ht="35.25" customHeight="1">
+      <c r="A1" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="H1" s="21" t="s">
+        <v>373</v>
+      </c>
+      <c r="I1" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="B1" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="22" t="s">
+      <c r="J1" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="K1" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="I1" s="22" t="s">
+      <c r="L1" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="J1" s="22" t="s">
+      <c r="M1" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="K1" s="22" t="s">
+      <c r="N1" s="21" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A2" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="L1" s="22" t="s">
+      <c r="B2" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="M1" s="22" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="23" t="s">
+      <c r="C2" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="D2" s="24" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="E2" s="24"/>
+      <c r="F2" s="25" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="G2" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="E2" s="25"/>
-      <c r="F2" s="26" t="s">
+      <c r="H2" s="25"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="G2" s="25" t="s">
+      <c r="N2" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25" t="s">
+    </row>
+    <row r="3" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A3" s="22"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="M2" s="25" t="s">
+      <c r="D3" s="26" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="23"/>
-      <c r="B3" s="24"/>
-      <c r="C3" s="27" t="s">
+      <c r="E3" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="F3" s="26" t="s">
         <v>115</v>
       </c>
-      <c r="E3" s="27" t="s">
+      <c r="G3" s="26"/>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27" t="s">
         <v>116</v>
       </c>
-      <c r="F3" s="27" t="s">
+      <c r="J3" s="26" t="s">
         <v>117</v>
       </c>
-      <c r="G3" s="27"/>
-      <c r="H3" s="28" t="s">
+      <c r="K3" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="I3" s="27" t="s">
+      <c r="L3" s="29" t="s">
         <v>119</v>
       </c>
-      <c r="J3" s="29" t="s">
+      <c r="M3" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="N3" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="K3" s="30" t="s">
+    </row>
+    <row r="4" spans="1:14" ht="51" customHeight="1">
+      <c r="A4" s="30"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="24" t="s">
         <v>121</v>
       </c>
-      <c r="L3" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="M3" s="27" t="s">
+      <c r="D4" s="24" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="4" ht="51.0" customHeight="1">
-      <c r="A4" s="31"/>
-      <c r="B4" s="32"/>
-      <c r="C4" s="25" t="s">
+      <c r="E4" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="F4" s="24" t="s">
         <v>123</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="G4" s="24"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="E4" s="25" t="s">
-        <v>116</v>
-      </c>
-      <c r="F4" s="25" t="s">
+      <c r="J4" s="24" t="s">
         <v>125</v>
       </c>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25" t="s">
+      <c r="K4" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="L4" s="32">
+        <f>8.5 * 1.578</f>
+        <v>13.413</v>
+      </c>
+      <c r="M4" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="N4" s="24" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A5" s="30"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="33" t="s">
         <v>126</v>
       </c>
-      <c r="I4" s="25" t="s">
+      <c r="L5" s="34">
+        <f>PI()*8.5*0.016</f>
+        <v>0.42725660088821188</v>
+      </c>
+      <c r="M5" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="J4" s="33" t="s">
-        <v>120</v>
-      </c>
-      <c r="K4" s="33">
-        <f> 8.5 * 1.578</f>
-        <v>13.413</v>
-      </c>
-      <c r="L4" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="M4" s="25" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="31"/>
-      <c r="B5" s="32"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25"/>
-      <c r="J5" s="34" t="s">
+      <c r="N5" s="24" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A6" s="30"/>
+      <c r="B6" s="35" t="s">
         <v>128</v>
       </c>
-      <c r="K5" s="35">
-        <f> PI()*8.5*0.016</f>
-        <v>0.4272566009</v>
-      </c>
-      <c r="L5" s="25" t="s">
+      <c r="C6" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="M5" s="25" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="31"/>
-      <c r="B6" s="36" t="s">
+      <c r="D6" s="26" t="s">
         <v>130</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="E6" s="26" t="s">
         <v>131</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="F6" s="26" t="s">
         <v>132</v>
       </c>
-      <c r="E6" s="27" t="s">
+      <c r="G6" s="26" t="s">
         <v>133</v>
       </c>
-      <c r="F6" s="27" t="s">
+      <c r="H6" s="27"/>
+      <c r="I6" s="26" t="s">
         <v>134</v>
       </c>
-      <c r="G6" s="27" t="s">
+      <c r="J6" s="26" t="s">
         <v>135</v>
       </c>
-      <c r="H6" s="27" t="s">
+      <c r="K6" s="26" t="s">
         <v>136</v>
       </c>
-      <c r="I6" s="27" t="s">
+      <c r="L6" s="36" t="s">
+        <v>119</v>
+      </c>
+      <c r="M6" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="N6" s="26" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A7" s="30"/>
+      <c r="B7" s="37"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="F7" s="38" t="s">
         <v>137</v>
       </c>
-      <c r="J6" s="27" t="s">
+      <c r="G7" s="26"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="38" t="s">
+        <v>137</v>
+      </c>
+      <c r="J7" s="38" t="s">
+        <v>137</v>
+      </c>
+      <c r="K7" s="39" t="s">
+        <v>137</v>
+      </c>
+      <c r="L7" s="38" t="s">
+        <v>137</v>
+      </c>
+      <c r="M7" s="38" t="s">
+        <v>137</v>
+      </c>
+      <c r="N7" s="26" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="60" customHeight="1">
+      <c r="A8" s="30"/>
+      <c r="B8" s="37"/>
+      <c r="C8" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="K6" s="37" t="s">
-        <v>121</v>
-      </c>
-      <c r="L6" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="M6" s="27" t="s">
+      <c r="D8" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>131</v>
+      </c>
+      <c r="F8" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="G8" s="24"/>
+      <c r="H8" s="25"/>
+      <c r="I8" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="J8" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="K8" s="32" t="s">
+        <v>142</v>
+      </c>
+      <c r="L8" s="40" t="s">
+        <v>119</v>
+      </c>
+      <c r="M8" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="N8" s="24" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="33.75" customHeight="1">
+      <c r="A9" s="30"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="31"/>
-      <c r="B7" s="38"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27" t="s">
-        <v>66</v>
-      </c>
-      <c r="F7" s="39" t="s">
-        <v>139</v>
-      </c>
-      <c r="G7" s="27"/>
-      <c r="H7" s="39" t="s">
-        <v>139</v>
-      </c>
-      <c r="I7" s="39" t="s">
-        <v>139</v>
-      </c>
-      <c r="J7" s="40" t="s">
-        <v>139</v>
-      </c>
-      <c r="K7" s="39" t="s">
-        <v>139</v>
-      </c>
-      <c r="L7" s="39" t="s">
-        <v>139</v>
-      </c>
-      <c r="M7" s="27" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" ht="60.0" customHeight="1">
-      <c r="A8" s="31"/>
-      <c r="B8" s="38"/>
-      <c r="C8" s="25" t="s">
-        <v>140</v>
-      </c>
-      <c r="D8" s="25" t="s">
-        <v>141</v>
-      </c>
-      <c r="E8" s="25" t="s">
-        <v>133</v>
-      </c>
-      <c r="F8" s="25" t="s">
-        <v>142</v>
-      </c>
-      <c r="G8" s="25"/>
-      <c r="H8" s="25" t="s">
+      <c r="F9" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="G9" s="24"/>
+      <c r="H9" s="25"/>
+      <c r="I9" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="J9" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="K9" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="L9" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="M9" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="N9" s="24" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="42.75" customHeight="1">
+      <c r="A10" s="30"/>
+      <c r="B10" s="37"/>
+      <c r="C10" s="26" t="s">
         <v>143</v>
       </c>
-      <c r="I8" s="25" t="s">
+      <c r="D10" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="F10" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="G10" s="26"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="26" t="s">
+        <v>146</v>
+      </c>
+      <c r="J10" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="K10" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="L10" s="36" t="s">
+        <v>119</v>
+      </c>
+      <c r="M10" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="N10" s="26" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="27.75" customHeight="1">
+      <c r="A11" s="30"/>
+      <c r="B11" s="37"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="38" t="s">
         <v>137</v>
       </c>
-      <c r="J8" s="33" t="s">
-        <v>144</v>
-      </c>
-      <c r="K8" s="41" t="s">
-        <v>121</v>
-      </c>
-      <c r="L8" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="M8" s="25" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="9" ht="33.75" customHeight="1">
-      <c r="A9" s="31"/>
-      <c r="B9" s="38"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="F9" s="42" t="s">
-        <v>139</v>
-      </c>
-      <c r="G9" s="25"/>
-      <c r="H9" s="42" t="s">
-        <v>139</v>
-      </c>
-      <c r="I9" s="42" t="s">
-        <v>139</v>
-      </c>
-      <c r="J9" s="42" t="s">
-        <v>139</v>
-      </c>
-      <c r="K9" s="42" t="s">
-        <v>139</v>
-      </c>
-      <c r="L9" s="42" t="s">
-        <v>139</v>
-      </c>
-      <c r="M9" s="25" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="10" ht="42.75" customHeight="1">
-      <c r="A10" s="31"/>
-      <c r="B10" s="38"/>
-      <c r="C10" s="27" t="s">
-        <v>145</v>
-      </c>
-      <c r="D10" s="27" t="s">
-        <v>146</v>
-      </c>
-      <c r="E10" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="F10" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="G10" s="27"/>
-      <c r="H10" s="27" t="s">
+      <c r="J11" s="38" t="s">
+        <v>137</v>
+      </c>
+      <c r="K11" s="39" t="s">
+        <v>137</v>
+      </c>
+      <c r="L11" s="38" t="s">
+        <v>137</v>
+      </c>
+      <c r="M11" s="38" t="s">
+        <v>137</v>
+      </c>
+      <c r="N11" s="26" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="45.75" customHeight="1">
+      <c r="A12" s="30"/>
+      <c r="B12" s="37"/>
+      <c r="C12" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="I10" s="27" t="s">
+      <c r="D12" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" s="24" t="s">
+        <v>150</v>
+      </c>
+      <c r="G12" s="24"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="J12" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="K12" s="32" t="s">
+        <v>152</v>
+      </c>
+      <c r="L12" s="33">
+        <f>7850*PI()*0.018^2*1/4</f>
+        <v>1.9975816887850697</v>
+      </c>
+      <c r="M12" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="N12" s="24" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="27.75" customHeight="1">
+      <c r="A13" s="30"/>
+      <c r="B13" s="37"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="F13" s="24"/>
+      <c r="G13" s="24"/>
+      <c r="H13" s="25"/>
+      <c r="I13" s="41" t="s">
         <v>137</v>
       </c>
-      <c r="J10" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="K10" s="37" t="s">
-        <v>121</v>
-      </c>
-      <c r="L10" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="M10" s="27" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="11" ht="27.75" customHeight="1">
-      <c r="A11" s="31"/>
-      <c r="B11" s="38"/>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="27" t="s">
-        <v>66</v>
-      </c>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="39" t="s">
-        <v>139</v>
-      </c>
-      <c r="I11" s="39" t="s">
-        <v>139</v>
-      </c>
-      <c r="J11" s="40" t="s">
-        <v>139</v>
-      </c>
-      <c r="K11" s="39" t="s">
-        <v>139</v>
-      </c>
-      <c r="L11" s="39" t="s">
-        <v>139</v>
-      </c>
-      <c r="M11" s="27" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="12" ht="45.75" customHeight="1">
-      <c r="A12" s="31"/>
-      <c r="B12" s="38"/>
-      <c r="C12" s="25" t="s">
-        <v>150</v>
-      </c>
-      <c r="D12" s="25" t="s">
-        <v>151</v>
-      </c>
-      <c r="E12" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="F12" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="G12" s="25"/>
-      <c r="H12" s="25" t="s">
+      <c r="J13" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="K13" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="L13" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="M13" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="N13" s="24" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="24.75" customHeight="1">
+      <c r="A14" s="30"/>
+      <c r="B14" s="37"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="25"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="32" t="s">
         <v>153</v>
       </c>
-      <c r="I12" s="25" t="s">
+      <c r="L14" s="34">
+        <f>PI()*0.018*1</f>
+        <v>5.654866776461627E-2</v>
+      </c>
+      <c r="M14" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="N14" s="24" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="39.75" customHeight="1">
+      <c r="A15" s="30"/>
+      <c r="B15" s="37"/>
+      <c r="C15" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="D15" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="E15" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="F15" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="G15" s="26"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="26" t="s">
+        <v>159</v>
+      </c>
+      <c r="J15" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="K15" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="L15" s="43" t="s">
+        <v>119</v>
+      </c>
+      <c r="M15" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="N15" s="26" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="31.5" customHeight="1">
+      <c r="A16" s="30"/>
+      <c r="B16" s="37"/>
+      <c r="C16" s="44" t="s">
+        <v>161</v>
+      </c>
+      <c r="D16" s="44" t="s">
+        <v>162</v>
+      </c>
+      <c r="E16" s="44" t="s">
+        <v>157</v>
+      </c>
+      <c r="F16" s="44" t="s">
+        <v>163</v>
+      </c>
+      <c r="G16" s="45"/>
+      <c r="H16" s="45"/>
+      <c r="I16" s="44" t="s">
+        <v>164</v>
+      </c>
+      <c r="J16" s="44" t="s">
+        <v>135</v>
+      </c>
+      <c r="K16" s="24" t="s">
+        <v>165</v>
+      </c>
+      <c r="L16" s="24">
+        <f>7850*1*0.1*0.01</f>
+        <v>7.8500000000000005</v>
+      </c>
+      <c r="M16" s="44" t="s">
+        <v>110</v>
+      </c>
+      <c r="N16" s="45" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="33" customHeight="1">
+      <c r="A17" s="30"/>
+      <c r="B17" s="37"/>
+      <c r="C17" s="44"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="44" t="s">
+        <v>167</v>
+      </c>
+      <c r="J17" s="44" t="s">
+        <v>135</v>
+      </c>
+      <c r="K17" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="L17" s="24">
+        <f>7850*1*0.06*0.008*2</f>
+        <v>7.5360000000000005</v>
+      </c>
+      <c r="M17" s="44" t="s">
+        <v>110</v>
+      </c>
+      <c r="N17" s="24" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A18" s="30"/>
+      <c r="B18" s="35"/>
+      <c r="C18" s="26" t="s">
+        <v>169</v>
+      </c>
+      <c r="D18" s="26" t="s">
+        <v>170</v>
+      </c>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26" t="s">
+        <v>171</v>
+      </c>
+      <c r="G18" s="26"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="J18" s="26"/>
+      <c r="K18" s="26"/>
+      <c r="L18" s="26"/>
+      <c r="M18" s="26"/>
+      <c r="N18" s="26" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A19" s="30"/>
+      <c r="B19" s="46" t="s">
+        <v>174</v>
+      </c>
+      <c r="C19" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="D19" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="E19" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="F19" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="G19" s="24" t="s">
+        <v>178</v>
+      </c>
+      <c r="H19" s="25"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="24"/>
+      <c r="K19" s="24" t="s">
+        <v>179</v>
+      </c>
+      <c r="L19" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="M19" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="N19" s="24" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A20" s="30"/>
+      <c r="B20" s="46"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="24"/>
+      <c r="K20" s="41" t="s">
         <v>137</v>
       </c>
-      <c r="J12" s="33" t="s">
-        <v>154</v>
-      </c>
-      <c r="K12" s="34">
-        <f>7850*PI()*0.018^2*1/4</f>
-        <v>1.997581689</v>
-      </c>
-      <c r="L12" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="M12" s="25" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="13" ht="27.75" customHeight="1">
-      <c r="A13" s="31"/>
-      <c r="B13" s="38"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25" t="s">
-        <v>85</v>
-      </c>
-      <c r="F13" s="25"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="42" t="s">
-        <v>139</v>
-      </c>
-      <c r="I13" s="42" t="s">
-        <v>139</v>
-      </c>
-      <c r="J13" s="42" t="s">
-        <v>139</v>
-      </c>
-      <c r="K13" s="42" t="s">
-        <v>139</v>
-      </c>
-      <c r="L13" s="42" t="s">
-        <v>139</v>
-      </c>
-      <c r="M13" s="25" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="14" ht="24.75" customHeight="1">
-      <c r="A14" s="31"/>
-      <c r="B14" s="38"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="F14" s="25"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="25"/>
-      <c r="I14" s="25"/>
-      <c r="J14" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="K14" s="35">
-        <f>PI()*0.018*1</f>
-        <v>0.05654866776</v>
-      </c>
-      <c r="L14" s="25" t="s">
-        <v>129</v>
-      </c>
-      <c r="M14" s="25" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="15" ht="39.75" customHeight="1">
-      <c r="A15" s="31"/>
-      <c r="B15" s="38"/>
-      <c r="C15" s="27" t="s">
+      <c r="L20" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="M20" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="N20" s="24" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A21" s="30"/>
+      <c r="B21" s="46"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="25"/>
+      <c r="I21" s="24"/>
+      <c r="J21" s="24"/>
+      <c r="K21" s="48" t="s">
+        <v>180</v>
+      </c>
+      <c r="L21" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="M21" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="N21" s="24" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A22" s="30"/>
+      <c r="B22" s="46"/>
+      <c r="C22" s="26" t="s">
+        <v>181</v>
+      </c>
+      <c r="D22" s="26" t="s">
+        <v>182</v>
+      </c>
+      <c r="E22" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="F22" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="G22" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="H22" s="27"/>
+      <c r="I22" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="J22" s="26" t="s">
+        <v>186</v>
+      </c>
+      <c r="K22" s="28" t="s">
+        <v>187</v>
+      </c>
+      <c r="L22" s="43" t="s">
+        <v>119</v>
+      </c>
+      <c r="M22" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="N22" s="26" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A23" s="30"/>
+      <c r="B23" s="31"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="38" t="s">
+        <v>137</v>
+      </c>
+      <c r="G23" s="26"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="38" t="s">
+        <v>137</v>
+      </c>
+      <c r="J23" s="38" t="s">
+        <v>137</v>
+      </c>
+      <c r="K23" s="38" t="s">
+        <v>137</v>
+      </c>
+      <c r="L23" s="38" t="s">
+        <v>137</v>
+      </c>
+      <c r="M23" s="38" t="s">
+        <v>137</v>
+      </c>
+      <c r="N23" s="49" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A24" s="30"/>
+      <c r="B24" s="31"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="F24" s="50" t="s">
+        <v>189</v>
+      </c>
+      <c r="G24" s="26"/>
+      <c r="H24" s="27"/>
+      <c r="I24" s="38"/>
+      <c r="J24" s="38"/>
+      <c r="K24" s="50" t="s">
+        <v>190</v>
+      </c>
+      <c r="L24" s="36" t="s">
+        <v>119</v>
+      </c>
+      <c r="M24" s="50" t="s">
+        <v>127</v>
+      </c>
+      <c r="N24" s="26" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="30.6" customHeight="1">
+      <c r="A25" s="30"/>
+      <c r="B25" s="31"/>
+      <c r="C25" s="24" t="s">
+        <v>191</v>
+      </c>
+      <c r="D25" s="24" t="s">
+        <v>192</v>
+      </c>
+      <c r="E25" s="24" t="s">
         <v>157</v>
       </c>
-      <c r="D15" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="E15" s="27" t="s">
-        <v>159</v>
-      </c>
-      <c r="F15" s="27" t="s">
-        <v>160</v>
-      </c>
-      <c r="G15" s="27"/>
-      <c r="H15" s="27" t="s">
-        <v>161</v>
-      </c>
-      <c r="I15" s="27" t="s">
+      <c r="F25" s="48" t="s">
+        <v>193</v>
+      </c>
+      <c r="G25" s="24"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="48" t="s">
+        <v>194</v>
+      </c>
+      <c r="J25" s="48" t="s">
+        <v>195</v>
+      </c>
+      <c r="K25" s="48" t="s">
+        <v>196</v>
+      </c>
+      <c r="L25" s="47">
+        <f>1.2 * 9.42</f>
+        <v>11.304</v>
+      </c>
+      <c r="M25" s="48" t="s">
+        <v>110</v>
+      </c>
+      <c r="N25" s="24" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A26" s="30"/>
+      <c r="B26" s="35" t="s">
+        <v>197</v>
+      </c>
+      <c r="C26" s="26" t="s">
+        <v>198</v>
+      </c>
+      <c r="D26" s="26" t="s">
+        <v>199</v>
+      </c>
+      <c r="E26" s="26" t="s">
+        <v>200</v>
+      </c>
+      <c r="F26" s="26" t="s">
+        <v>201</v>
+      </c>
+      <c r="G26" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="H26" s="27"/>
+      <c r="I26" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="J26" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="K26" s="26" t="s">
+        <v>205</v>
+      </c>
+      <c r="L26" s="36" t="s">
+        <v>119</v>
+      </c>
+      <c r="M26" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="N26" s="26" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A27" s="30"/>
+      <c r="B27" s="37"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="F27" s="38" t="s">
         <v>137</v>
       </c>
-      <c r="J15" s="27" t="s">
-        <v>162</v>
-      </c>
-      <c r="K15" s="44" t="s">
-        <v>121</v>
-      </c>
-      <c r="L15" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="M15" s="27" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="16" ht="31.5" customHeight="1">
-      <c r="A16" s="31"/>
-      <c r="B16" s="38"/>
-      <c r="C16" s="45" t="s">
-        <v>163</v>
-      </c>
-      <c r="D16" s="45" t="s">
-        <v>164</v>
-      </c>
-      <c r="E16" s="45" t="s">
-        <v>159</v>
-      </c>
-      <c r="F16" s="45" t="s">
-        <v>165</v>
-      </c>
-      <c r="G16" s="46"/>
-      <c r="H16" s="45" t="s">
-        <v>166</v>
-      </c>
-      <c r="I16" s="45" t="s">
+      <c r="G27" s="26"/>
+      <c r="H27" s="27"/>
+      <c r="I27" s="38" t="s">
         <v>137</v>
       </c>
-      <c r="J16" s="25" t="s">
-        <v>167</v>
-      </c>
-      <c r="K16" s="25">
-        <f> 7850*1*0.1*0.01</f>
-        <v>7.85</v>
-      </c>
-      <c r="L16" s="45" t="s">
-        <v>112</v>
-      </c>
-      <c r="M16" s="46" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="17" ht="33.0" customHeight="1">
-      <c r="A17" s="31"/>
-      <c r="B17" s="38"/>
-      <c r="C17" s="45"/>
-      <c r="D17" s="45"/>
-      <c r="E17" s="45" t="s">
-        <v>168</v>
-      </c>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="45" t="s">
-        <v>169</v>
-      </c>
-      <c r="I17" s="45" t="s">
+      <c r="J27" s="38" t="s">
         <v>137</v>
       </c>
-      <c r="J17" s="25" t="s">
-        <v>170</v>
-      </c>
-      <c r="K17" s="25">
-        <f> 7850*1*0.06*0.008*2</f>
-        <v>7.536</v>
-      </c>
-      <c r="L17" s="45" t="s">
-        <v>112</v>
-      </c>
-      <c r="M17" s="25" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="31"/>
-      <c r="B18" s="36"/>
-      <c r="C18" s="27" t="s">
-        <v>171</v>
-      </c>
-      <c r="D18" s="27" t="s">
-        <v>172</v>
-      </c>
-      <c r="E18" s="27"/>
-      <c r="F18" s="27" t="s">
-        <v>173</v>
-      </c>
-      <c r="G18" s="27"/>
-      <c r="H18" s="27" t="s">
-        <v>174</v>
-      </c>
-      <c r="I18" s="27"/>
-      <c r="J18" s="27"/>
-      <c r="K18" s="27"/>
-      <c r="L18" s="27"/>
-      <c r="M18" s="27" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="31"/>
-      <c r="B19" s="47" t="s">
-        <v>176</v>
-      </c>
-      <c r="C19" s="25" t="s">
-        <v>177</v>
-      </c>
-      <c r="D19" s="25" t="s">
-        <v>178</v>
-      </c>
-      <c r="E19" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="F19" s="25" t="s">
-        <v>179</v>
-      </c>
-      <c r="G19" s="25" t="s">
-        <v>180</v>
-      </c>
-      <c r="H19" s="25"/>
-      <c r="I19" s="25"/>
-      <c r="J19" s="25" t="s">
-        <v>181</v>
-      </c>
-      <c r="K19" s="48" t="s">
-        <v>121</v>
-      </c>
-      <c r="L19" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="M19" s="25" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="31"/>
-      <c r="B20" s="47"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25" t="s">
-        <v>85</v>
-      </c>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="25"/>
-      <c r="I20" s="25"/>
-      <c r="J20" s="42" t="s">
-        <v>139</v>
-      </c>
-      <c r="K20" s="42" t="s">
-        <v>139</v>
-      </c>
-      <c r="L20" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="M20" s="25" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="31"/>
-      <c r="B21" s="47"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="25"/>
-      <c r="I21" s="25"/>
-      <c r="J21" s="49" t="s">
-        <v>182</v>
-      </c>
-      <c r="K21" s="48" t="s">
-        <v>121</v>
-      </c>
-      <c r="L21" s="25" t="s">
-        <v>129</v>
-      </c>
-      <c r="M21" s="25" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="31"/>
-      <c r="B22" s="47"/>
-      <c r="C22" s="27" t="s">
-        <v>183</v>
-      </c>
-      <c r="D22" s="27" t="s">
-        <v>184</v>
-      </c>
-      <c r="E22" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="F22" s="27" t="s">
-        <v>185</v>
-      </c>
-      <c r="G22" s="27" t="s">
-        <v>186</v>
-      </c>
-      <c r="H22" s="27" t="s">
-        <v>187</v>
-      </c>
-      <c r="I22" s="27" t="s">
-        <v>188</v>
-      </c>
-      <c r="J22" s="29" t="s">
-        <v>189</v>
-      </c>
-      <c r="K22" s="44" t="s">
-        <v>121</v>
-      </c>
-      <c r="L22" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="M22" s="27" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="31"/>
-      <c r="B23" s="32"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="F23" s="39" t="s">
-        <v>139</v>
-      </c>
-      <c r="G23" s="27"/>
-      <c r="H23" s="39" t="s">
-        <v>139</v>
-      </c>
-      <c r="I23" s="39" t="s">
-        <v>139</v>
-      </c>
-      <c r="J23" s="39" t="s">
-        <v>139</v>
-      </c>
-      <c r="K23" s="39" t="s">
-        <v>139</v>
-      </c>
-      <c r="L23" s="39" t="s">
-        <v>139</v>
-      </c>
-      <c r="M23" s="50" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="31"/>
-      <c r="B24" s="32"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="F24" s="51" t="s">
-        <v>191</v>
-      </c>
-      <c r="G24" s="27"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="39"/>
-      <c r="J24" s="51" t="s">
-        <v>192</v>
-      </c>
-      <c r="K24" s="37" t="s">
-        <v>121</v>
-      </c>
-      <c r="L24" s="51" t="s">
-        <v>129</v>
-      </c>
-      <c r="M24" s="27" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="31"/>
-      <c r="B25" s="32"/>
-      <c r="C25" s="25" t="s">
-        <v>193</v>
-      </c>
-      <c r="D25" s="25" t="s">
-        <v>194</v>
-      </c>
-      <c r="E25" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="F25" s="49" t="s">
-        <v>195</v>
-      </c>
-      <c r="G25" s="25"/>
-      <c r="H25" s="49" t="s">
-        <v>196</v>
-      </c>
-      <c r="I25" s="49" t="s">
-        <v>197</v>
-      </c>
-      <c r="J25" s="49" t="s">
-        <v>198</v>
-      </c>
-      <c r="K25" s="48">
-        <f> 1.2 * 9.42</f>
-        <v>11.304</v>
-      </c>
-      <c r="L25" s="49" t="s">
-        <v>112</v>
-      </c>
-      <c r="M25" s="25" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="31"/>
-      <c r="B26" s="36" t="s">
-        <v>199</v>
-      </c>
-      <c r="C26" s="27" t="s">
-        <v>200</v>
-      </c>
-      <c r="D26" s="27" t="s">
-        <v>201</v>
-      </c>
-      <c r="E26" s="27" t="s">
-        <v>202</v>
-      </c>
-      <c r="F26" s="27" t="s">
-        <v>203</v>
-      </c>
-      <c r="G26" s="27" t="s">
-        <v>204</v>
-      </c>
-      <c r="H26" s="27" t="s">
-        <v>205</v>
-      </c>
-      <c r="I26" s="27" t="s">
+      <c r="K27" s="38" t="s">
+        <v>137</v>
+      </c>
+      <c r="L27" s="38" t="s">
+        <v>137</v>
+      </c>
+      <c r="M27" s="38" t="s">
+        <v>137</v>
+      </c>
+      <c r="N27" s="26" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A28" s="30"/>
+      <c r="B28" s="37"/>
+      <c r="C28" s="24" t="s">
         <v>206</v>
       </c>
-      <c r="J26" s="27" t="s">
+      <c r="D28" s="24" t="s">
         <v>207</v>
       </c>
-      <c r="K26" s="37" t="s">
-        <v>121</v>
-      </c>
-      <c r="L26" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="M26" s="27" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="31"/>
-      <c r="B27" s="38"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="F27" s="39" t="s">
-        <v>139</v>
-      </c>
-      <c r="G27" s="27"/>
-      <c r="H27" s="39" t="s">
-        <v>139</v>
-      </c>
-      <c r="I27" s="39" t="s">
-        <v>139</v>
-      </c>
-      <c r="J27" s="39" t="s">
-        <v>139</v>
-      </c>
-      <c r="K27" s="39" t="s">
-        <v>139</v>
-      </c>
-      <c r="L27" s="39" t="s">
-        <v>139</v>
-      </c>
-      <c r="M27" s="27" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="31"/>
-      <c r="B28" s="38"/>
-      <c r="C28" s="25" t="s">
+      <c r="E28" s="24" t="s">
         <v>208</v>
       </c>
-      <c r="D28" s="25" t="s">
+      <c r="F28" s="24" t="s">
         <v>209</v>
       </c>
-      <c r="E28" s="25" t="s">
+      <c r="G28" s="24"/>
+      <c r="H28" s="25"/>
+      <c r="I28" s="24" t="s">
         <v>210</v>
       </c>
-      <c r="F28" s="25" t="s">
+      <c r="J28" s="24" t="s">
         <v>211</v>
       </c>
-      <c r="G28" s="25"/>
-      <c r="H28" s="25" t="s">
+      <c r="K28" s="24"/>
+      <c r="L28" s="24"/>
+      <c r="M28" s="24"/>
+      <c r="N28" s="24" t="s">
         <v>212</v>
       </c>
-      <c r="I28" s="25" t="s">
+    </row>
+    <row r="29" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A29" s="30"/>
+      <c r="B29" s="35"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="24" t="s">
         <v>213</v>
       </c>
-      <c r="J28" s="25"/>
-      <c r="K28" s="25"/>
-      <c r="L28" s="25"/>
-      <c r="M28" s="25" t="s">
+      <c r="F29" s="24"/>
+      <c r="G29" s="24"/>
+      <c r="H29" s="25"/>
+      <c r="I29" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="J29" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="K29" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="L29" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="M29" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="N29" s="24" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="31"/>
-      <c r="B29" s="36"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="25" t="s">
+    <row r="30" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A30" s="30"/>
+      <c r="B30" s="35"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="24"/>
+      <c r="E30" s="24" t="s">
         <v>215</v>
       </c>
-      <c r="F29" s="25"/>
-      <c r="G29" s="25"/>
-      <c r="H29" s="42" t="s">
-        <v>139</v>
-      </c>
-      <c r="I29" s="42" t="s">
-        <v>139</v>
-      </c>
-      <c r="J29" s="42" t="s">
-        <v>139</v>
-      </c>
-      <c r="K29" s="42" t="s">
-        <v>139</v>
-      </c>
-      <c r="L29" s="42" t="s">
-        <v>139</v>
-      </c>
-      <c r="M29" s="25" t="s">
+      <c r="F30" s="24"/>
+      <c r="G30" s="24"/>
+      <c r="H30" s="25"/>
+      <c r="I30" s="24"/>
+      <c r="J30" s="24"/>
+      <c r="K30" s="24"/>
+      <c r="L30" s="51">
+        <v>2.1199999999999999E-11</v>
+      </c>
+      <c r="M30" s="24" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="31"/>
-      <c r="B30" s="36"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="25" t="s">
+      <c r="N30" s="24" t="s">
         <v>217</v>
       </c>
-      <c r="F30" s="25"/>
-      <c r="G30" s="25"/>
-      <c r="H30" s="25"/>
-      <c r="I30" s="25"/>
-      <c r="J30" s="25"/>
-      <c r="K30" s="52">
-        <v>2.12E-11</v>
-      </c>
-      <c r="L30" s="25" t="s">
+    </row>
+    <row r="31" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A31" s="52"/>
+      <c r="B31" s="53"/>
+      <c r="C31" s="54"/>
+      <c r="D31" s="54"/>
+      <c r="E31" s="54" t="s">
         <v>218</v>
       </c>
-      <c r="M30" s="25" t="s">
+      <c r="F31" s="54"/>
+      <c r="G31" s="54"/>
+      <c r="H31" s="54"/>
+      <c r="I31" s="54"/>
+      <c r="J31" s="54"/>
+      <c r="K31" s="54"/>
+      <c r="L31" s="55" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="53"/>
-      <c r="B31" s="54"/>
-      <c r="C31" s="55"/>
-      <c r="D31" s="55"/>
-      <c r="E31" s="55" t="s">
+      <c r="M31" s="54" t="s">
+        <v>110</v>
+      </c>
+      <c r="N31" s="54" t="s">
         <v>220</v>
       </c>
-      <c r="F31" s="55"/>
-      <c r="G31" s="55"/>
-      <c r="H31" s="55"/>
-      <c r="I31" s="55"/>
-      <c r="J31" s="55"/>
-      <c r="K31" s="56" t="s">
-        <v>221</v>
-      </c>
-      <c r="L31" s="55" t="s">
-        <v>112</v>
-      </c>
-      <c r="M31" s="55" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="57"/>
-      <c r="B32" s="57"/>
-      <c r="C32" s="57"/>
-      <c r="D32" s="57"/>
-      <c r="E32" s="57"/>
-      <c r="F32" s="57"/>
-      <c r="G32" s="57"/>
-      <c r="H32" s="57"/>
-      <c r="I32" s="57"/>
-      <c r="J32" s="57"/>
-      <c r="K32" s="57"/>
-      <c r="L32" s="57"/>
-      <c r="M32" s="57"/>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="57"/>
-      <c r="B33" s="57"/>
-      <c r="C33" s="57"/>
-      <c r="D33" s="57"/>
-      <c r="E33" s="57"/>
-      <c r="F33" s="57"/>
-      <c r="G33" s="57"/>
-      <c r="H33" s="57"/>
-      <c r="I33" s="57"/>
-      <c r="J33" s="57"/>
-      <c r="K33" s="57"/>
-      <c r="L33" s="57"/>
-      <c r="M33" s="57"/>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="57"/>
-      <c r="B34" s="57"/>
-      <c r="C34" s="57"/>
-      <c r="D34" s="57"/>
-      <c r="E34" s="57"/>
-      <c r="F34" s="57"/>
-      <c r="G34" s="57"/>
-      <c r="H34" s="57"/>
-      <c r="I34" s="57"/>
-      <c r="J34" s="57"/>
-      <c r="K34" s="57"/>
-      <c r="L34" s="57"/>
-      <c r="M34" s="57"/>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="57"/>
-      <c r="B35" s="57"/>
-      <c r="C35" s="57"/>
-      <c r="D35" s="57"/>
-      <c r="E35" s="57"/>
-      <c r="F35" s="57"/>
-      <c r="G35" s="57"/>
-      <c r="H35" s="57"/>
-      <c r="I35" s="57"/>
-      <c r="J35" s="57"/>
-      <c r="K35" s="57"/>
-      <c r="L35" s="57"/>
-      <c r="M35" s="57"/>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="57"/>
-      <c r="B36" s="57"/>
-      <c r="C36" s="57"/>
-      <c r="D36" s="57"/>
-      <c r="E36" s="57"/>
-      <c r="F36" s="57"/>
-      <c r="G36" s="57"/>
-      <c r="H36" s="57"/>
-      <c r="I36" s="57"/>
-      <c r="J36" s="57"/>
-      <c r="K36" s="57"/>
-      <c r="L36" s="57"/>
-      <c r="M36" s="57"/>
-    </row>
-    <row r="37" ht="15.75" customHeight="1"/>
-    <row r="38" ht="15.75" customHeight="1"/>
-    <row r="39" ht="15.75" customHeight="1"/>
-    <row r="40" ht="15.75" customHeight="1"/>
-    <row r="41" ht="15.75" customHeight="1"/>
-    <row r="42" ht="15.75" customHeight="1"/>
-    <row r="43" ht="15.75" customHeight="1"/>
-    <row r="44" ht="15.75" customHeight="1"/>
-    <row r="45" ht="15.75" customHeight="1"/>
-    <row r="46" ht="15.75" customHeight="1"/>
-    <row r="47" ht="15.75" customHeight="1"/>
-    <row r="48" ht="15.75" customHeight="1"/>
+    </row>
+    <row r="32" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A32" s="56"/>
+      <c r="B32" s="56"/>
+      <c r="C32" s="56"/>
+      <c r="D32" s="56"/>
+      <c r="E32" s="56"/>
+      <c r="F32" s="56"/>
+      <c r="G32" s="56"/>
+      <c r="H32" s="56"/>
+      <c r="I32" s="56"/>
+      <c r="J32" s="56"/>
+      <c r="K32" s="56"/>
+      <c r="L32" s="56"/>
+      <c r="M32" s="56"/>
+      <c r="N32" s="56"/>
+    </row>
+    <row r="33" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A33" s="56"/>
+      <c r="B33" s="56"/>
+      <c r="C33" s="56"/>
+      <c r="D33" s="56"/>
+      <c r="E33" s="56"/>
+      <c r="F33" s="56"/>
+      <c r="G33" s="56"/>
+      <c r="H33" s="56"/>
+      <c r="I33" s="56"/>
+      <c r="J33" s="56"/>
+      <c r="K33" s="56"/>
+      <c r="L33" s="56"/>
+      <c r="M33" s="56"/>
+      <c r="N33" s="56"/>
+    </row>
+    <row r="34" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A34" s="56"/>
+      <c r="B34" s="56"/>
+      <c r="C34" s="56"/>
+      <c r="D34" s="56"/>
+      <c r="E34" s="56"/>
+      <c r="F34" s="56"/>
+      <c r="G34" s="56"/>
+      <c r="H34" s="56"/>
+      <c r="I34" s="56"/>
+      <c r="J34" s="56"/>
+      <c r="K34" s="56"/>
+      <c r="L34" s="56"/>
+      <c r="M34" s="56"/>
+      <c r="N34" s="56"/>
+    </row>
+    <row r="35" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A35" s="56"/>
+      <c r="B35" s="56"/>
+      <c r="C35" s="56"/>
+      <c r="D35" s="56"/>
+      <c r="E35" s="56"/>
+      <c r="F35" s="56"/>
+      <c r="G35" s="56"/>
+      <c r="H35" s="56"/>
+      <c r="I35" s="56"/>
+      <c r="J35" s="56"/>
+      <c r="K35" s="56"/>
+      <c r="L35" s="56"/>
+      <c r="M35" s="56"/>
+      <c r="N35" s="56"/>
+    </row>
+    <row r="36" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A36" s="56"/>
+      <c r="B36" s="56"/>
+      <c r="C36" s="56"/>
+      <c r="D36" s="56"/>
+      <c r="E36" s="56"/>
+      <c r="F36" s="56"/>
+      <c r="G36" s="56"/>
+      <c r="H36" s="56"/>
+      <c r="I36" s="56"/>
+      <c r="J36" s="56"/>
+      <c r="K36" s="56"/>
+      <c r="L36" s="56"/>
+      <c r="M36" s="56"/>
+      <c r="N36" s="56"/>
+    </row>
+    <row r="37" spans="1:14" ht="15.75" customHeight="1"/>
+    <row r="38" spans="1:14" ht="15.75" customHeight="1"/>
+    <row r="39" spans="1:14" ht="15.75" customHeight="1"/>
+    <row r="40" spans="1:14" ht="15.75" customHeight="1"/>
+    <row r="41" spans="1:14" ht="15.75" customHeight="1"/>
+    <row r="42" spans="1:14" ht="15.75" customHeight="1"/>
+    <row r="43" spans="1:14" ht="15.75" customHeight="1"/>
+    <row r="44" spans="1:14" ht="15.75" customHeight="1"/>
+    <row r="45" spans="1:14" ht="15.75" customHeight="1"/>
+    <row r="46" spans="1:14" ht="15.75" customHeight="1"/>
+    <row r="47" spans="1:14" ht="15.75" customHeight="1"/>
+    <row r="48" spans="1:14" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>
@@ -5806,27 +6947,28 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <dimension ref="A1:G1000"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="12.13"/>
-    <col customWidth="1" min="2" max="5" width="12.63"/>
-    <col customWidth="1" min="6" max="6" width="27.13"/>
-    <col customWidth="1" min="7" max="7" width="40.38"/>
+    <col min="1" max="1" width="12.109375" customWidth="1"/>
+    <col min="2" max="5" width="12.6640625" customWidth="1"/>
+    <col min="6" max="6" width="27.109375" customWidth="1"/>
+    <col min="7" max="7" width="40.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1" spans="1:7" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -5847,581 +6989,581 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="58" t="s">
+    <row r="2" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A2" s="57" t="s">
+        <v>221</v>
+      </c>
+      <c r="B2" s="58" t="s">
+        <v>222</v>
+      </c>
+      <c r="C2" s="59" t="s">
         <v>223</v>
       </c>
-      <c r="B2" s="59" t="s">
+      <c r="D2" s="59" t="s">
         <v>224</v>
       </c>
-      <c r="C2" s="60" t="s">
+      <c r="E2" s="59" t="s">
         <v>225</v>
       </c>
-      <c r="D2" s="60" t="s">
+      <c r="F2" s="60" t="s">
         <v>226</v>
       </c>
-      <c r="E2" s="60" t="s">
+      <c r="G2" s="59" t="s">
         <v>227</v>
       </c>
-      <c r="F2" s="61" t="s">
+    </row>
+    <row r="3" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A3" s="61"/>
+      <c r="B3" s="62" t="s">
         <v>228</v>
       </c>
-      <c r="G2" s="60" t="s">
+      <c r="C3" s="63" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="62"/>
-      <c r="B3" s="63" t="s">
+      <c r="D3" s="63" t="s">
         <v>230</v>
       </c>
-      <c r="C3" s="64" t="s">
+      <c r="E3" s="63" t="s">
         <v>231</v>
       </c>
-      <c r="D3" s="64" t="s">
+      <c r="F3" s="63" t="s">
         <v>232</v>
       </c>
-      <c r="E3" s="64" t="s">
+      <c r="G3" s="63" t="s">
         <v>233</v>
       </c>
-      <c r="F3" s="64" t="s">
+    </row>
+    <row r="4" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A4" s="61"/>
+      <c r="B4" s="58" t="s">
         <v>234</v>
       </c>
-      <c r="G3" s="64" t="s">
+      <c r="C4" s="59" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="62"/>
-      <c r="B4" s="59" t="s">
+      <c r="D4" s="59" t="s">
         <v>236</v>
       </c>
-      <c r="C4" s="60" t="s">
+      <c r="E4" s="59" t="s">
         <v>237</v>
       </c>
-      <c r="D4" s="60" t="s">
+      <c r="F4" s="60" t="s">
         <v>238</v>
       </c>
-      <c r="E4" s="60" t="s">
+      <c r="G4" s="59" t="s">
         <v>239</v>
       </c>
-      <c r="F4" s="61" t="s">
+    </row>
+    <row r="5" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A5" s="61"/>
+      <c r="B5" s="62" t="s">
         <v>240</v>
       </c>
-      <c r="G4" s="60" t="s">
+      <c r="C5" s="63" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="62"/>
-      <c r="B5" s="63" t="s">
+      <c r="D5" s="63" t="s">
         <v>242</v>
       </c>
-      <c r="C5" s="64" t="s">
+      <c r="E5" s="63" t="s">
         <v>243</v>
       </c>
-      <c r="D5" s="64" t="s">
+      <c r="F5" s="63"/>
+      <c r="G5" s="63" t="s">
         <v>244</v>
       </c>
-      <c r="E5" s="64" t="s">
+    </row>
+    <row r="6" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A6" s="61"/>
+      <c r="B6" s="62" t="s">
         <v>245</v>
       </c>
-      <c r="F5" s="64"/>
-      <c r="G5" s="64" t="s">
+      <c r="C6" s="64"/>
+      <c r="D6" s="63"/>
+      <c r="E6" s="63" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="62"/>
-      <c r="B6" s="63" t="s">
+      <c r="F6" s="63"/>
+      <c r="G6" s="63" t="s">
         <v>247</v>
       </c>
-      <c r="C6" s="65"/>
-      <c r="D6" s="64"/>
-      <c r="E6" s="64" t="s">
+    </row>
+    <row r="7" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A7" s="61"/>
+      <c r="B7" s="62" t="s">
         <v>248</v>
       </c>
-      <c r="F6" s="64"/>
-      <c r="G6" s="64" t="s">
+      <c r="C7" s="64"/>
+      <c r="D7" s="63"/>
+      <c r="E7" s="63" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="62"/>
-      <c r="B7" s="63" t="s">
+      <c r="F7" s="63"/>
+      <c r="G7" s="63" t="s">
         <v>250</v>
       </c>
-      <c r="C7" s="65"/>
-      <c r="D7" s="64"/>
-      <c r="E7" s="64" t="s">
+    </row>
+    <row r="8" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A8" s="61"/>
+      <c r="B8" s="65"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="63" t="s">
         <v>251</v>
       </c>
-      <c r="F7" s="64"/>
-      <c r="G7" s="64" t="s">
+      <c r="F8" s="63"/>
+      <c r="G8" s="63" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="62"/>
-      <c r="B8" s="66"/>
-      <c r="C8" s="65"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="64" t="s">
+    <row r="9" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A9" s="61"/>
+      <c r="B9" s="65"/>
+      <c r="C9" s="64"/>
+      <c r="D9" s="63"/>
+      <c r="E9" s="63" t="s">
         <v>253</v>
       </c>
-      <c r="F8" s="64"/>
-      <c r="G8" s="64" t="s">
+      <c r="F9" s="63"/>
+      <c r="G9" s="63" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="62"/>
-      <c r="B9" s="66"/>
-      <c r="C9" s="65"/>
-      <c r="D9" s="64"/>
-      <c r="E9" s="64" t="s">
+    <row r="10" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A10" s="61"/>
+      <c r="B10" s="65"/>
+      <c r="C10" s="64"/>
+      <c r="D10" s="63"/>
+      <c r="E10" s="63" t="s">
         <v>255</v>
       </c>
-      <c r="F9" s="64"/>
-      <c r="G9" s="64" t="s">
+      <c r="F10" s="63"/>
+      <c r="G10" s="63" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="62"/>
-      <c r="B10" s="66"/>
-      <c r="C10" s="65"/>
-      <c r="D10" s="64"/>
-      <c r="E10" s="64" t="s">
+    <row r="11" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A11" s="61"/>
+      <c r="B11" s="65"/>
+      <c r="C11" s="64"/>
+      <c r="D11" s="63"/>
+      <c r="E11" s="63" t="s">
         <v>257</v>
       </c>
-      <c r="F10" s="64"/>
-      <c r="G10" s="64" t="s">
+      <c r="F11" s="63"/>
+      <c r="G11" s="63" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="62"/>
-      <c r="B11" s="66"/>
-      <c r="C11" s="65"/>
-      <c r="D11" s="64"/>
-      <c r="E11" s="64" t="s">
+    <row r="12" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A12" s="61"/>
+      <c r="B12" s="65"/>
+      <c r="C12" s="59" t="s">
         <v>259</v>
       </c>
-      <c r="F11" s="64"/>
-      <c r="G11" s="64" t="s">
+      <c r="D12" s="59" t="s">
+        <v>259</v>
+      </c>
+      <c r="E12" s="59" t="s">
+        <v>259</v>
+      </c>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="62"/>
-      <c r="B12" s="66"/>
-      <c r="C12" s="60" t="s">
+    <row r="13" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A13" s="61"/>
+      <c r="B13" s="65"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="59" t="s">
         <v>261</v>
       </c>
-      <c r="D12" s="60" t="s">
-        <v>261</v>
-      </c>
-      <c r="E12" s="60" t="s">
-        <v>261</v>
-      </c>
-      <c r="F12" s="60"/>
-      <c r="G12" s="60" t="s">
+      <c r="F13" s="59"/>
+      <c r="G13" s="59" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="62"/>
-      <c r="B13" s="66"/>
-      <c r="C13" s="67"/>
-      <c r="D13" s="60"/>
-      <c r="E13" s="60" t="s">
+    <row r="14" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A14" s="61"/>
+      <c r="B14" s="65"/>
+      <c r="C14" s="63" t="s">
         <v>263</v>
       </c>
-      <c r="F13" s="60"/>
-      <c r="G13" s="60" t="s">
+      <c r="D14" s="63" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="62"/>
-      <c r="B14" s="66"/>
-      <c r="C14" s="64" t="s">
+      <c r="E14" s="63" t="s">
         <v>265</v>
       </c>
-      <c r="D14" s="64" t="s">
+      <c r="F14" s="63"/>
+      <c r="G14" s="63" t="s">
         <v>266</v>
       </c>
-      <c r="E14" s="64" t="s">
+    </row>
+    <row r="15" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A15" s="61"/>
+      <c r="B15" s="65"/>
+      <c r="C15" s="64"/>
+      <c r="D15" s="63"/>
+      <c r="E15" s="63" t="s">
         <v>267</v>
       </c>
-      <c r="F14" s="64"/>
-      <c r="G14" s="64" t="s">
+      <c r="F15" s="63"/>
+      <c r="G15" s="63" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="62"/>
-      <c r="B15" s="66"/>
-      <c r="C15" s="65"/>
-      <c r="D15" s="64"/>
-      <c r="E15" s="64" t="s">
+    <row r="16" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A16" s="61"/>
+      <c r="B16" s="65"/>
+      <c r="C16" s="64"/>
+      <c r="D16" s="63"/>
+      <c r="E16" s="63" t="s">
         <v>269</v>
       </c>
-      <c r="F15" s="64"/>
-      <c r="G15" s="64" t="s">
+      <c r="F16" s="63"/>
+      <c r="G16" s="63" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="62"/>
-      <c r="B16" s="66"/>
-      <c r="C16" s="65"/>
-      <c r="D16" s="64"/>
-      <c r="E16" s="64" t="s">
+    <row r="17" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A17" s="61"/>
+      <c r="B17" s="65"/>
+      <c r="C17" s="64"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="63" t="s">
         <v>271</v>
       </c>
-      <c r="F16" s="64"/>
-      <c r="G16" s="64" t="s">
+      <c r="F17" s="63"/>
+      <c r="G17" s="63" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="62"/>
-      <c r="B17" s="66"/>
-      <c r="C17" s="65"/>
-      <c r="D17" s="64"/>
-      <c r="E17" s="64" t="s">
+    <row r="18" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A18" s="61"/>
+      <c r="B18" s="65"/>
+      <c r="C18" s="59" t="s">
         <v>273</v>
       </c>
-      <c r="F17" s="64"/>
-      <c r="G17" s="64" t="s">
+      <c r="D18" s="59" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="62"/>
-      <c r="B18" s="66"/>
-      <c r="C18" s="60" t="s">
+      <c r="E18" s="59" t="s">
         <v>275</v>
       </c>
-      <c r="D18" s="60" t="s">
+      <c r="F18" s="59"/>
+      <c r="G18" s="59" t="s">
         <v>276</v>
       </c>
-      <c r="E18" s="60" t="s">
+    </row>
+    <row r="19" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A19" s="61"/>
+      <c r="B19" s="65"/>
+      <c r="C19" s="66"/>
+      <c r="D19" s="59"/>
+      <c r="E19" s="59" t="s">
         <v>277</v>
       </c>
-      <c r="F18" s="60"/>
-      <c r="G18" s="60" t="s">
+      <c r="F19" s="59"/>
+      <c r="G19" s="59" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="62"/>
-      <c r="B19" s="66"/>
-      <c r="C19" s="67"/>
-      <c r="D19" s="60"/>
-      <c r="E19" s="60" t="s">
+    <row r="20" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A20" s="61"/>
+      <c r="B20" s="65"/>
+      <c r="C20" s="63" t="s">
         <v>279</v>
       </c>
-      <c r="F19" s="60"/>
-      <c r="G19" s="60" t="s">
+      <c r="D20" s="63" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="62"/>
-      <c r="B20" s="66"/>
-      <c r="C20" s="64" t="s">
+      <c r="E20" s="63" t="s">
         <v>281</v>
       </c>
-      <c r="D20" s="64" t="s">
+      <c r="F20" s="63"/>
+      <c r="G20" s="63" t="s">
         <v>282</v>
       </c>
-      <c r="E20" s="64" t="s">
+    </row>
+    <row r="21" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A21" s="61"/>
+      <c r="B21" s="65"/>
+      <c r="C21" s="59" t="s">
         <v>283</v>
       </c>
-      <c r="F20" s="64"/>
-      <c r="G20" s="64" t="s">
+      <c r="D21" s="59" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="62"/>
-      <c r="B21" s="66"/>
-      <c r="C21" s="60" t="s">
+      <c r="E21" s="59" t="s">
+        <v>283</v>
+      </c>
+      <c r="F21" s="59"/>
+      <c r="G21" s="59" t="s">
         <v>285</v>
       </c>
-      <c r="D21" s="60" t="s">
+    </row>
+    <row r="22" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A22" s="61"/>
+      <c r="B22" s="65"/>
+      <c r="C22" s="66"/>
+      <c r="D22" s="59"/>
+      <c r="E22" s="59" t="s">
         <v>286</v>
       </c>
-      <c r="E21" s="60" t="s">
-        <v>285</v>
-      </c>
-      <c r="F21" s="60"/>
-      <c r="G21" s="60" t="s">
+      <c r="F22" s="59"/>
+      <c r="G22" s="59" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="62"/>
-      <c r="B22" s="66"/>
-      <c r="C22" s="67"/>
-      <c r="D22" s="60"/>
-      <c r="E22" s="60" t="s">
+    <row r="23" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A23" s="61"/>
+      <c r="B23" s="65"/>
+      <c r="C23" s="66"/>
+      <c r="D23" s="59"/>
+      <c r="E23" s="59" t="s">
         <v>288</v>
       </c>
-      <c r="F22" s="60"/>
-      <c r="G22" s="60" t="s">
+      <c r="F23" s="59"/>
+      <c r="G23" s="59" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="62"/>
-      <c r="B23" s="66"/>
-      <c r="C23" s="67"/>
-      <c r="D23" s="60"/>
-      <c r="E23" s="60" t="s">
+    <row r="24" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A24" s="61"/>
+      <c r="B24" s="58" t="s">
         <v>290</v>
       </c>
-      <c r="F23" s="60"/>
-      <c r="G23" s="60" t="s">
+      <c r="C24" s="63" t="s">
+        <v>290</v>
+      </c>
+      <c r="D24" s="63" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="62"/>
-      <c r="B24" s="59" t="s">
+      <c r="E24" s="63" t="s">
         <v>292</v>
       </c>
-      <c r="C24" s="64" t="s">
-        <v>292</v>
-      </c>
-      <c r="D24" s="64" t="s">
+      <c r="F24" s="67" t="s">
         <v>293</v>
       </c>
-      <c r="E24" s="64" t="s">
+      <c r="G24" s="63" t="s">
         <v>294</v>
       </c>
-      <c r="F24" s="68" t="s">
+    </row>
+    <row r="25" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A25" s="61"/>
+      <c r="B25" s="68"/>
+      <c r="C25" s="64"/>
+      <c r="D25" s="63"/>
+      <c r="E25" s="63" t="s">
         <v>295</v>
       </c>
-      <c r="G24" s="64" t="s">
+      <c r="F25" s="63"/>
+      <c r="G25" s="63" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A26" s="61"/>
+      <c r="B26" s="68"/>
+      <c r="C26" s="64"/>
+      <c r="D26" s="63"/>
+      <c r="E26" s="63" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="62"/>
-      <c r="B25" s="69"/>
-      <c r="C25" s="65"/>
-      <c r="D25" s="64"/>
-      <c r="E25" s="64" t="s">
+      <c r="F26" s="63"/>
+      <c r="G26" s="63" t="s">
         <v>297</v>
       </c>
-      <c r="F25" s="64"/>
-      <c r="G25" s="64" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="62"/>
-      <c r="B26" s="69"/>
-      <c r="C26" s="65"/>
-      <c r="D26" s="64"/>
-      <c r="E26" s="64" t="s">
+    </row>
+    <row r="27" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A27" s="61"/>
+      <c r="B27" s="68"/>
+      <c r="C27" s="59" t="s">
         <v>298</v>
       </c>
-      <c r="F26" s="64"/>
-      <c r="G26" s="64" t="s">
+      <c r="D27" s="59" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="62"/>
-      <c r="B27" s="69"/>
-      <c r="C27" s="60" t="s">
+      <c r="E27" s="59" t="s">
         <v>300</v>
       </c>
-      <c r="D27" s="60" t="s">
+      <c r="F27" s="60" t="s">
         <v>301</v>
       </c>
-      <c r="E27" s="60" t="s">
+      <c r="G27" s="59" t="s">
         <v>302</v>
       </c>
-      <c r="F27" s="61" t="s">
+    </row>
+    <row r="28" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A28" s="61"/>
+      <c r="B28" s="68"/>
+      <c r="C28" s="66"/>
+      <c r="D28" s="59"/>
+      <c r="E28" s="59" t="s">
+        <v>271</v>
+      </c>
+      <c r="F28" s="59"/>
+      <c r="G28" s="59" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A29" s="61"/>
+      <c r="B29" s="68"/>
+      <c r="C29" s="66"/>
+      <c r="D29" s="59"/>
+      <c r="E29" s="59" t="s">
+        <v>267</v>
+      </c>
+      <c r="F29" s="59"/>
+      <c r="G29" s="59" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A30" s="61"/>
+      <c r="B30" s="62" t="s">
         <v>303</v>
       </c>
-      <c r="G27" s="60" t="s">
+      <c r="C30" s="63" t="s">
+        <v>198</v>
+      </c>
+      <c r="D30" s="63" t="s">
+        <v>199</v>
+      </c>
+      <c r="E30" s="63" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="62"/>
-      <c r="B28" s="69"/>
-      <c r="C28" s="67"/>
-      <c r="D28" s="60"/>
-      <c r="E28" s="60" t="s">
-        <v>273</v>
-      </c>
-      <c r="F28" s="60"/>
-      <c r="G28" s="60" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="62"/>
-      <c r="B29" s="69"/>
-      <c r="C29" s="67"/>
-      <c r="D29" s="60"/>
-      <c r="E29" s="60" t="s">
-        <v>269</v>
-      </c>
-      <c r="F29" s="60"/>
-      <c r="G29" s="60" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="62"/>
-      <c r="B30" s="63" t="s">
+      <c r="F30" s="67" t="s">
         <v>305</v>
       </c>
-      <c r="C30" s="64" t="s">
-        <v>200</v>
-      </c>
-      <c r="D30" s="64" t="s">
-        <v>201</v>
-      </c>
-      <c r="E30" s="64" t="s">
+      <c r="G30" s="63" t="s">
         <v>306</v>
       </c>
-      <c r="F30" s="68" t="s">
+    </row>
+    <row r="31" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A31" s="61"/>
+      <c r="B31" s="65"/>
+      <c r="C31" s="64"/>
+      <c r="D31" s="63"/>
+      <c r="E31" s="63" t="s">
         <v>307</v>
       </c>
-      <c r="G30" s="64" t="s">
+      <c r="F31" s="63"/>
+      <c r="G31" s="63" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A32" s="61"/>
+      <c r="B32" s="58" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="62"/>
-      <c r="B31" s="66"/>
-      <c r="C31" s="65"/>
-      <c r="D31" s="64"/>
-      <c r="E31" s="64" t="s">
+      <c r="C32" s="66"/>
+      <c r="D32" s="59" t="s">
         <v>309</v>
       </c>
-      <c r="F31" s="64"/>
-      <c r="G31" s="64" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="62"/>
-      <c r="B32" s="59" t="s">
+      <c r="E32" s="59" t="s">
         <v>310</v>
       </c>
-      <c r="C32" s="67"/>
-      <c r="D32" s="60" t="s">
+      <c r="F32" s="60" t="s">
         <v>311</v>
       </c>
-      <c r="E32" s="60" t="s">
+      <c r="G32" s="59" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A33" s="61"/>
+      <c r="B33" s="62" t="s">
         <v>312</v>
       </c>
-      <c r="F32" s="61" t="s">
+      <c r="C33" s="63" t="s">
         <v>313</v>
       </c>
-      <c r="G32" s="60" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="62"/>
-      <c r="B33" s="63" t="s">
+      <c r="D33" s="64" t="s">
         <v>314</v>
       </c>
-      <c r="C33" s="64" t="s">
+      <c r="E33" s="64"/>
+      <c r="F33" s="64"/>
+      <c r="G33" s="63" t="s">
         <v>315</v>
       </c>
-      <c r="D33" s="65" t="s">
+    </row>
+    <row r="34" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A34" s="61"/>
+      <c r="B34" s="65"/>
+      <c r="C34" s="63" t="s">
         <v>316</v>
       </c>
-      <c r="E33" s="65"/>
-      <c r="F33" s="65"/>
-      <c r="G33" s="64" t="s">
+      <c r="D34" s="64" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="62"/>
-      <c r="B34" s="66"/>
-      <c r="C34" s="64" t="s">
+      <c r="E34" s="64"/>
+      <c r="F34" s="64"/>
+      <c r="G34" s="63" t="s">
         <v>318</v>
       </c>
-      <c r="D34" s="65" t="s">
+    </row>
+    <row r="35" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A35" s="61"/>
+      <c r="B35" s="65"/>
+      <c r="C35" s="63" t="s">
         <v>319</v>
       </c>
-      <c r="E34" s="65"/>
-      <c r="F34" s="65"/>
-      <c r="G34" s="64" t="s">
+      <c r="D35" s="64" t="s">
+        <v>319</v>
+      </c>
+      <c r="E35" s="64"/>
+      <c r="F35" s="64"/>
+      <c r="G35" s="63" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="62"/>
-      <c r="B35" s="66"/>
-      <c r="C35" s="64" t="s">
+    <row r="36" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A36" s="61"/>
+      <c r="B36" s="65"/>
+      <c r="C36" s="63" t="s">
         <v>321</v>
       </c>
-      <c r="D35" s="65" t="s">
-        <v>321</v>
-      </c>
-      <c r="E35" s="65"/>
-      <c r="F35" s="65"/>
-      <c r="G35" s="64" t="s">
+      <c r="D36" s="64" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="62"/>
-      <c r="B36" s="66"/>
-      <c r="C36" s="64" t="s">
+      <c r="E36" s="64"/>
+      <c r="F36" s="64"/>
+      <c r="G36" s="63" t="s">
         <v>323</v>
       </c>
-      <c r="D36" s="65" t="s">
+    </row>
+    <row r="37" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A37" s="61"/>
+      <c r="B37" s="69"/>
+      <c r="C37" s="70" t="s">
         <v>324</v>
       </c>
-      <c r="E36" s="65"/>
-      <c r="F36" s="65"/>
-      <c r="G36" s="64" t="s">
+      <c r="D37" s="71" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="62"/>
-      <c r="B37" s="70"/>
-      <c r="C37" s="71" t="s">
+      <c r="E37" s="71"/>
+      <c r="F37" s="71"/>
+      <c r="G37" s="70" t="s">
         <v>326</v>
       </c>
-      <c r="D37" s="72" t="s">
-        <v>327</v>
-      </c>
-      <c r="E37" s="72"/>
-      <c r="F37" s="72"/>
-      <c r="G37" s="71" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="38" ht="15.75" customHeight="1"/>
-    <row r="39" ht="15.75" customHeight="1"/>
-    <row r="40" ht="15.75" customHeight="1"/>
-    <row r="41" ht="15.75" customHeight="1"/>
-    <row r="42" ht="15.75" customHeight="1"/>
-    <row r="43" ht="15.75" customHeight="1"/>
-    <row r="44" ht="15.75" customHeight="1"/>
-    <row r="45" ht="15.75" customHeight="1"/>
-    <row r="46" ht="15.75" customHeight="1"/>
-    <row r="47" ht="15.75" customHeight="1"/>
-    <row r="48" ht="15.75" customHeight="1"/>
+    </row>
+    <row r="38" spans="1:7" ht="15.75" customHeight="1"/>
+    <row r="39" spans="1:7" ht="15.75" customHeight="1"/>
+    <row r="40" spans="1:7" ht="15.75" customHeight="1"/>
+    <row r="41" spans="1:7" ht="15.75" customHeight="1"/>
+    <row r="42" spans="1:7" ht="15.75" customHeight="1"/>
+    <row r="43" spans="1:7" ht="15.75" customHeight="1"/>
+    <row r="44" spans="1:7" ht="15.75" customHeight="1"/>
+    <row r="45" spans="1:7" ht="15.75" customHeight="1"/>
+    <row r="46" spans="1:7" ht="15.75" customHeight="1"/>
+    <row r="47" spans="1:7" ht="15.75" customHeight="1"/>
+    <row r="48" spans="1:7" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>
@@ -7375,232 +8517,233 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <dimension ref="A1:J1000"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="5" width="12.63"/>
+    <col min="1" max="5" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="73" t="s">
+    <row r="1" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A1" s="72" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1" s="72" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1" s="72" t="s">
         <v>329</v>
       </c>
-      <c r="B1" s="73" t="s">
+      <c r="D1" s="72" t="s">
         <v>330</v>
       </c>
-      <c r="C1" s="73" t="s">
+      <c r="E1" s="72" t="s">
         <v>331</v>
       </c>
-      <c r="D1" s="73" t="s">
+      <c r="F1" s="72" t="s">
         <v>332</v>
       </c>
-      <c r="E1" s="73" t="s">
+      <c r="G1" s="72" t="s">
         <v>333</v>
       </c>
-      <c r="F1" s="73" t="s">
+      <c r="H1" s="72" t="s">
         <v>334</v>
       </c>
-      <c r="G1" s="73" t="s">
+      <c r="I1" s="72" t="s">
         <v>335</v>
       </c>
-      <c r="H1" s="73" t="s">
+      <c r="J1" s="72" t="s">
         <v>336</v>
       </c>
-      <c r="I1" s="73" t="s">
-        <v>337</v>
-      </c>
-      <c r="J1" s="73" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="73">
-        <v>12.0</v>
-      </c>
-      <c r="B2" s="73">
-        <v>2.0</v>
-      </c>
-      <c r="C2" s="73">
+    </row>
+    <row r="2" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A2" s="72">
+        <v>12</v>
+      </c>
+      <c r="B2" s="72">
+        <v>2</v>
+      </c>
+      <c r="C2" s="72">
         <f>1.2/50*6</f>
-        <v>0.144</v>
-      </c>
-      <c r="D2" s="73">
+        <v>0.14400000000000002</v>
+      </c>
+      <c r="D2" s="72">
         <f>33.3/1000*6</f>
-        <v>0.1998</v>
-      </c>
-      <c r="E2" s="73">
+        <v>0.19979999999999998</v>
+      </c>
+      <c r="E2" s="72">
         <f>1.01*5</f>
         <v>5.05</v>
       </c>
-      <c r="F2" s="73">
+      <c r="F2" s="72">
         <f>0.1*24</f>
-        <v>2.4</v>
-      </c>
-      <c r="G2" s="73">
+        <v>2.4000000000000004</v>
+      </c>
+      <c r="G2" s="72">
         <f>8/100*54</f>
         <v>4.32</v>
       </c>
-      <c r="H2" s="73">
+      <c r="H2" s="72">
         <f>0.008*10</f>
         <v>0.08</v>
       </c>
-      <c r="I2" s="73">
-        <f t="shared" ref="I2:I4" si="1">C2+D2+E2+F2+G2+H2</f>
-        <v>12.1938</v>
-      </c>
-      <c r="J2" s="73">
-        <f t="shared" ref="J2:J4" si="2">I2*60/1000</f>
-        <v>0.731628</v>
-      </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="73">
-        <v>18.0</v>
-      </c>
-      <c r="B3" s="73">
+      <c r="I2" s="72">
+        <f t="shared" ref="I2:I4" si="0">C2+D2+E2+F2+G2+H2</f>
+        <v>12.193800000000001</v>
+      </c>
+      <c r="J2" s="72">
+        <f t="shared" ref="J2:J4" si="1">I2*60/1000</f>
+        <v>0.73162800000000006</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A3" s="72">
+        <v>18</v>
+      </c>
+      <c r="B3" s="72">
         <v>2.8</v>
       </c>
-      <c r="C3" s="73">
-        <f t="shared" ref="C3:C4" si="3">2.9/50*6</f>
-        <v>0.348</v>
-      </c>
-      <c r="D3" s="73">
-        <f t="shared" ref="D3:D4" si="4">64.4/1000*6</f>
-        <v>0.3864</v>
-      </c>
-      <c r="E3" s="73">
+      <c r="C3" s="72">
+        <f t="shared" ref="C3:C4" si="2">2.9/50*6</f>
+        <v>0.34799999999999998</v>
+      </c>
+      <c r="D3" s="72">
+        <f t="shared" ref="D3:D4" si="3">64.4/1000*6</f>
+        <v>0.38639999999999997</v>
+      </c>
+      <c r="E3" s="72">
         <f>1.33*5</f>
         <v>6.65</v>
       </c>
-      <c r="F3" s="73">
+      <c r="F3" s="72">
         <f>19*0.19+5*0.14</f>
-        <v>4.31</v>
-      </c>
-      <c r="G3" s="73">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="G3" s="72">
         <f>8/100*78</f>
         <v>6.24</v>
       </c>
-      <c r="H3" s="73">
+      <c r="H3" s="72">
         <f>0.008*21</f>
-        <v>0.168</v>
-      </c>
-      <c r="I3" s="73">
+        <v>0.16800000000000001</v>
+      </c>
+      <c r="I3" s="72">
+        <f t="shared" si="0"/>
+        <v>18.102399999999999</v>
+      </c>
+      <c r="J3" s="72">
         <f t="shared" si="1"/>
-        <v>18.1024</v>
-      </c>
-      <c r="J3" s="73">
+        <v>1.086144</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A4" s="72">
+        <v>24</v>
+      </c>
+      <c r="B4" s="72">
+        <v>3.36</v>
+      </c>
+      <c r="C4" s="72">
         <f t="shared" si="2"/>
-        <v>1.086144</v>
-      </c>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="73">
-        <v>24.0</v>
-      </c>
-      <c r="B4" s="73">
-        <v>3.36</v>
-      </c>
-      <c r="C4" s="73">
+        <v>0.34799999999999998</v>
+      </c>
+      <c r="D4" s="72">
         <f t="shared" si="3"/>
-        <v>0.348</v>
-      </c>
-      <c r="D4" s="73">
-        <f t="shared" si="4"/>
-        <v>0.3864</v>
-      </c>
-      <c r="E4" s="73">
+        <v>0.38639999999999997</v>
+      </c>
+      <c r="E4" s="72">
         <f>5*1.81</f>
-        <v>9.05</v>
-      </c>
-      <c r="F4" s="73">
+        <v>9.0500000000000007</v>
+      </c>
+      <c r="F4" s="72">
         <f>24*0.19</f>
-        <v>4.56</v>
-      </c>
-      <c r="G4" s="73">
+        <v>4.5600000000000005</v>
+      </c>
+      <c r="G4" s="72">
         <f>8/100*108</f>
         <v>8.64</v>
       </c>
-      <c r="H4" s="73">
-        <f> 0.008*31</f>
+      <c r="H4" s="72">
+        <f>0.008*31</f>
         <v>0.248</v>
       </c>
-      <c r="I4" s="73">
+      <c r="I4" s="72">
+        <f t="shared" si="0"/>
+        <v>23.232400000000002</v>
+      </c>
+      <c r="J4" s="72">
         <f t="shared" si="1"/>
-        <v>23.2324</v>
-      </c>
-      <c r="J4" s="73">
-        <f t="shared" si="2"/>
-        <v>1.393944</v>
-      </c>
-    </row>
-    <row r="5" ht="15.75" customHeight="1"/>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="73"/>
-      <c r="B6" s="73"/>
-    </row>
-    <row r="7" ht="15.75" customHeight="1"/>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="73"/>
-      <c r="B8" s="73"/>
-      <c r="C8" s="73"/>
-    </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="73"/>
-      <c r="B9" s="73"/>
-      <c r="C9" s="73"/>
-    </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="73"/>
-      <c r="B10" s="73"/>
-      <c r="C10" s="73"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="73"/>
-      <c r="B11" s="73"/>
-      <c r="C11" s="73"/>
-    </row>
-    <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="73"/>
-      <c r="B12" s="73"/>
-      <c r="C12" s="73"/>
-    </row>
-    <row r="13" ht="15.75" customHeight="1"/>
-    <row r="14" ht="15.75" customHeight="1"/>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="B15" s="73"/>
-      <c r="C15" s="73"/>
-    </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="73"/>
-    </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="73"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="73"/>
-    </row>
-    <row r="19" ht="15.75" customHeight="1"/>
-    <row r="20" ht="15.75" customHeight="1"/>
-    <row r="21" ht="15.75" customHeight="1"/>
-    <row r="22" ht="15.75" customHeight="1"/>
-    <row r="23" ht="15.75" customHeight="1"/>
-    <row r="24" ht="15.75" customHeight="1"/>
-    <row r="25" ht="15.75" customHeight="1"/>
-    <row r="26" ht="15.75" customHeight="1"/>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1"/>
+        <v>1.3939440000000003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="6" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A6" s="72"/>
+      <c r="B6" s="72"/>
+    </row>
+    <row r="7" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="8" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A8" s="72"/>
+      <c r="B8" s="72"/>
+      <c r="C8" s="72"/>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A9" s="72"/>
+      <c r="B9" s="72"/>
+      <c r="C9" s="72"/>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A10" s="72"/>
+      <c r="B10" s="72"/>
+      <c r="C10" s="72"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A11" s="72"/>
+      <c r="B11" s="72"/>
+      <c r="C11" s="72"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A12" s="72"/>
+      <c r="B12" s="72"/>
+      <c r="C12" s="72"/>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="14" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="15" spans="1:10" ht="15.75" customHeight="1">
+      <c r="B15" s="72"/>
+      <c r="C15" s="72"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A16" s="72"/>
+    </row>
+    <row r="17" spans="1:1" ht="15.75" customHeight="1">
+      <c r="A17" s="72"/>
+    </row>
+    <row r="18" spans="1:1" ht="15.75" customHeight="1">
+      <c r="A18" s="72"/>
+    </row>
+    <row r="19" spans="1:1" ht="15.75" customHeight="1"/>
+    <row r="20" spans="1:1" ht="15.75" customHeight="1"/>
+    <row r="21" spans="1:1" ht="15.75" customHeight="1"/>
+    <row r="22" spans="1:1" ht="15.75" customHeight="1"/>
+    <row r="23" spans="1:1" ht="15.75" customHeight="1"/>
+    <row r="24" spans="1:1" ht="15.75" customHeight="1"/>
+    <row r="25" spans="1:1" ht="15.75" customHeight="1"/>
+    <row r="26" spans="1:1" ht="15.75" customHeight="1"/>
+    <row r="27" spans="1:1" ht="15.75" customHeight="1"/>
+    <row r="28" spans="1:1" ht="15.75" customHeight="1"/>
+    <row r="29" spans="1:1" ht="15.75" customHeight="1"/>
+    <row r="30" spans="1:1" ht="15.75" customHeight="1"/>
+    <row r="31" spans="1:1" ht="15.75" customHeight="1"/>
+    <row r="32" spans="1:1" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>
@@ -8570,693 +9713,698 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <dimension ref="A1:I998"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="2" width="12.63"/>
-    <col customWidth="1" min="3" max="3" width="21.63"/>
-    <col customWidth="1" min="4" max="4" width="22.38"/>
-    <col customWidth="1" min="5" max="5" width="22.25"/>
-    <col customWidth="1" min="6" max="6" width="12.63"/>
+    <col min="1" max="2" width="12.6640625" customWidth="1"/>
+    <col min="3" max="3" width="21.6640625" customWidth="1"/>
+    <col min="4" max="4" width="22.33203125" customWidth="1"/>
+    <col min="5" max="5" width="22.21875" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="74" t="s">
+    <row r="1" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A1" s="73" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1" s="73" t="s">
+        <v>338</v>
+      </c>
+      <c r="C1" s="73" t="s">
         <v>339</v>
       </c>
-      <c r="B1" s="74" t="s">
+      <c r="D1" s="73" t="s">
         <v>340</v>
       </c>
-      <c r="C1" s="74" t="s">
+      <c r="E1" s="73" t="s">
         <v>341</v>
       </c>
-      <c r="D1" s="74" t="s">
+      <c r="F1" s="73" t="s">
         <v>342</v>
       </c>
-      <c r="E1" s="74" t="s">
+      <c r="H1" s="72" t="s">
         <v>343</v>
       </c>
-      <c r="F1" s="74" t="s">
+      <c r="I1" s="72">
+        <v>7850</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A2" s="74"/>
+      <c r="B2" s="75"/>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+    </row>
+    <row r="3" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A3" s="74" t="s">
         <v>344</v>
       </c>
-      <c r="H1" s="73" t="s">
+      <c r="B3" s="74" t="s">
         <v>345</v>
       </c>
-      <c r="I1" s="73">
-        <v>7850.0</v>
-      </c>
-    </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="75"/>
-      <c r="B2" s="76"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-    </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="75" t="s">
+      <c r="C3" s="76" t="s">
+        <v>345</v>
+      </c>
+      <c r="D3" s="76" t="s">
+        <v>345</v>
+      </c>
+      <c r="E3" s="74" t="s">
         <v>346</v>
       </c>
-      <c r="B3" s="75" t="s">
+      <c r="F3" s="74" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A4" s="76" t="s">
         <v>347</v>
       </c>
-      <c r="C3" s="77" t="s">
+      <c r="B4" s="74">
+        <f t="shared" ref="B4:D4" si="0">PI()*0.012^2/4*1.5*$I$1</f>
+        <v>1.3317211258567134</v>
+      </c>
+      <c r="C4" s="74">
+        <f t="shared" si="0"/>
+        <v>1.3317211258567134</v>
+      </c>
+      <c r="D4" s="74">
+        <f t="shared" si="0"/>
+        <v>1.3317211258567134</v>
+      </c>
+      <c r="E4" s="74">
+        <f t="shared" ref="E4:F4" si="1">PI()*0.014^2/4*2*$I$1</f>
+        <v>2.4168272284066283</v>
+      </c>
+      <c r="F4" s="74">
+        <f t="shared" si="1"/>
+        <v>2.4168272284066283</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A5" s="74" t="s">
+        <v>348</v>
+      </c>
+      <c r="B5" s="75">
+        <v>48</v>
+      </c>
+      <c r="C5" s="75">
+        <v>48</v>
+      </c>
+      <c r="D5" s="75">
+        <v>48</v>
+      </c>
+      <c r="E5" s="77">
+        <v>60</v>
+      </c>
+      <c r="F5" s="77">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A6" s="76" t="s">
         <v>347</v>
       </c>
-      <c r="D3" s="77" t="s">
+      <c r="B6" s="75">
+        <f t="shared" ref="B6:D6" si="2">0.0173*B5</f>
+        <v>0.83040000000000003</v>
+      </c>
+      <c r="C6" s="75">
+        <f t="shared" si="2"/>
+        <v>0.83040000000000003</v>
+      </c>
+      <c r="D6" s="75">
+        <f t="shared" si="2"/>
+        <v>0.83040000000000003</v>
+      </c>
+      <c r="E6" s="75">
+        <f t="shared" ref="E6:F6" si="3">0.025*E5</f>
+        <v>1.5</v>
+      </c>
+      <c r="F6" s="75">
+        <f t="shared" si="3"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A7" s="74" t="s">
+        <v>349</v>
+      </c>
+      <c r="B7" s="75">
+        <v>12</v>
+      </c>
+      <c r="C7" s="75">
+        <v>12</v>
+      </c>
+      <c r="D7" s="75">
+        <v>12</v>
+      </c>
+      <c r="E7" s="75">
+        <v>23</v>
+      </c>
+      <c r="F7" s="75">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A8" s="76" t="s">
         <v>347</v>
       </c>
-      <c r="E3" s="75" t="s">
-        <v>348</v>
-      </c>
-      <c r="F3" s="75" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="77" t="s">
-        <v>349</v>
-      </c>
-      <c r="B4" s="75">
-        <f t="shared" ref="B4:D4" si="1">PI()*0.012^2/4*1.5*$I$1</f>
-        <v>1.331721126</v>
-      </c>
-      <c r="C4" s="75">
-        <f t="shared" si="1"/>
-        <v>1.331721126</v>
-      </c>
-      <c r="D4" s="75">
-        <f t="shared" si="1"/>
-        <v>1.331721126</v>
-      </c>
-      <c r="E4" s="75">
-        <f t="shared" ref="E4:F4" si="2">PI()*0.014^2/4*2*$I$1</f>
-        <v>2.416827228</v>
-      </c>
-      <c r="F4" s="75">
-        <f t="shared" si="2"/>
-        <v>2.416827228</v>
-      </c>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="75" t="s">
+      <c r="B8" s="75">
+        <f t="shared" ref="B8:F8" si="4">0.01*B7</f>
+        <v>0.12</v>
+      </c>
+      <c r="C8" s="75">
+        <f t="shared" si="4"/>
+        <v>0.12</v>
+      </c>
+      <c r="D8" s="75">
+        <f t="shared" si="4"/>
+        <v>0.12</v>
+      </c>
+      <c r="E8" s="75">
+        <f t="shared" si="4"/>
+        <v>0.23</v>
+      </c>
+      <c r="F8" s="75">
+        <f t="shared" si="4"/>
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A9" s="74" t="s">
         <v>350</v>
       </c>
-      <c r="B5" s="76">
-        <v>48.0</v>
-      </c>
-      <c r="C5" s="76">
-        <v>48.0</v>
-      </c>
-      <c r="D5" s="76">
-        <v>48.0</v>
-      </c>
-      <c r="E5" s="78">
-        <v>60.0</v>
-      </c>
-      <c r="F5" s="78">
-        <v>60.0</v>
-      </c>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="77" t="s">
-        <v>349</v>
-      </c>
-      <c r="B6" s="76">
-        <f t="shared" ref="B6:D6" si="3">0.0173*B5</f>
-        <v>0.8304</v>
-      </c>
-      <c r="C6" s="76">
-        <f t="shared" si="3"/>
-        <v>0.8304</v>
-      </c>
-      <c r="D6" s="76">
-        <f t="shared" si="3"/>
-        <v>0.8304</v>
-      </c>
-      <c r="E6" s="76">
-        <f t="shared" ref="E6:F6" si="4">0.025*E5</f>
-        <v>1.5</v>
-      </c>
-      <c r="F6" s="76">
-        <f t="shared" si="4"/>
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="75" t="s">
+      <c r="B9" s="74" t="s">
         <v>351</v>
       </c>
-      <c r="B7" s="76">
-        <v>12.0</v>
-      </c>
-      <c r="C7" s="76">
-        <v>12.0</v>
-      </c>
-      <c r="D7" s="76">
-        <v>12.0</v>
-      </c>
-      <c r="E7" s="76">
-        <v>23.0</v>
-      </c>
-      <c r="F7" s="76">
-        <v>23.0</v>
-      </c>
-    </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="77" t="s">
-        <v>349</v>
-      </c>
-      <c r="B8" s="76">
-        <f t="shared" ref="B8:F8" si="5">0.01*B7</f>
-        <v>0.12</v>
-      </c>
-      <c r="C8" s="76">
-        <f t="shared" si="5"/>
-        <v>0.12</v>
-      </c>
-      <c r="D8" s="76">
-        <f t="shared" si="5"/>
-        <v>0.12</v>
-      </c>
-      <c r="E8" s="76">
-        <f t="shared" si="5"/>
-        <v>0.23</v>
-      </c>
-      <c r="F8" s="76">
-        <f t="shared" si="5"/>
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="75" t="s">
+      <c r="C9" s="74" t="s">
         <v>352</v>
       </c>
-      <c r="B9" s="75" t="s">
+      <c r="D9" s="74" t="s">
+        <v>352</v>
+      </c>
+      <c r="E9" s="74" t="s">
         <v>353</v>
       </c>
-      <c r="C9" s="75" t="s">
+      <c r="F9" s="74" t="s">
         <v>354</v>
       </c>
-      <c r="D9" s="75" t="s">
-        <v>354</v>
-      </c>
-      <c r="E9" s="75" t="s">
+    </row>
+    <row r="10" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A10" s="74" t="s">
         <v>355</v>
       </c>
-      <c r="F9" s="75" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="75" t="s">
-        <v>357</v>
-      </c>
-      <c r="B10" s="76">
-        <v>42.0</v>
-      </c>
-      <c r="C10" s="76">
-        <v>54.0</v>
-      </c>
-      <c r="D10" s="76">
-        <v>66.0</v>
-      </c>
-      <c r="E10" s="76">
-        <v>66.0</v>
-      </c>
-      <c r="F10" s="76">
-        <v>78.0</v>
-      </c>
-    </row>
-    <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="77" t="s">
-        <v>349</v>
-      </c>
-      <c r="B11" s="76">
+      <c r="B10" s="75">
+        <v>42</v>
+      </c>
+      <c r="C10" s="75">
+        <v>54</v>
+      </c>
+      <c r="D10" s="75">
+        <v>66</v>
+      </c>
+      <c r="E10" s="75">
+        <v>66</v>
+      </c>
+      <c r="F10" s="75">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A11" s="76" t="s">
+        <v>347</v>
+      </c>
+      <c r="B11" s="75">
         <f>0.00472*B10</f>
         <v>0.19824</v>
       </c>
-      <c r="C11" s="76">
-        <f t="shared" ref="C11:D11" si="6">0.00575*C10</f>
+      <c r="C11" s="75">
+        <f t="shared" ref="C11:D11" si="5">0.00575*C10</f>
         <v>0.3105</v>
       </c>
-      <c r="D11" s="76">
+      <c r="D11" s="75">
+        <f t="shared" si="5"/>
+        <v>0.3795</v>
+      </c>
+      <c r="E11" s="75">
+        <f>0.00679*E10</f>
+        <v>0.44813999999999998</v>
+      </c>
+      <c r="F11" s="75">
+        <f>0.00835*F10</f>
+        <v>0.65129999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A12" s="78" t="s">
+        <v>356</v>
+      </c>
+      <c r="B12" s="79">
+        <f t="shared" ref="B12:F12" si="6">SUM(B4,B6,B8,B11)</f>
+        <v>2.4803611258567138</v>
+      </c>
+      <c r="C12" s="79">
         <f t="shared" si="6"/>
-        <v>0.3795</v>
-      </c>
-      <c r="E11" s="76">
-        <f>0.00679*E10</f>
-        <v>0.44814</v>
-      </c>
-      <c r="F11" s="76">
-        <f>0.00835*F10</f>
-        <v>0.6513</v>
-      </c>
-    </row>
-    <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="79" t="s">
+        <v>2.5926211258567138</v>
+      </c>
+      <c r="D12" s="79">
+        <f t="shared" si="6"/>
+        <v>2.6616211258567137</v>
+      </c>
+      <c r="E12" s="79">
+        <f t="shared" si="6"/>
+        <v>4.5949672284066292</v>
+      </c>
+      <c r="F12" s="79">
+        <f t="shared" si="6"/>
+        <v>4.7981272284066288</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A13" s="74"/>
+      <c r="B13" s="74"/>
+      <c r="C13" s="75"/>
+      <c r="D13" s="74"/>
+      <c r="E13" s="74"/>
+      <c r="F13" s="74"/>
+    </row>
+    <row r="14" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A14" s="74" t="s">
+        <v>357</v>
+      </c>
+      <c r="B14" s="76" t="s">
         <v>358</v>
       </c>
-      <c r="B12" s="80">
-        <f t="shared" ref="B12:F12" si="7">SUM(B4,B6,B8,B11)</f>
-        <v>2.480361126</v>
-      </c>
-      <c r="C12" s="80">
+      <c r="C14" s="76" t="s">
+        <v>358</v>
+      </c>
+      <c r="D14" s="76" t="s">
+        <v>358</v>
+      </c>
+      <c r="E14" s="76" t="s">
+        <v>359</v>
+      </c>
+      <c r="F14" s="76" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A15" s="76" t="s">
+        <v>347</v>
+      </c>
+      <c r="B15" s="76">
+        <f t="shared" ref="B15:F15" si="7">PI()*0.012^2/4*0.04*4*$I$1</f>
+        <v>0.14205025342471608</v>
+      </c>
+      <c r="C15" s="76">
         <f t="shared" si="7"/>
-        <v>2.592621126</v>
-      </c>
-      <c r="D12" s="80">
+        <v>0.14205025342471608</v>
+      </c>
+      <c r="D15" s="76">
         <f t="shared" si="7"/>
-        <v>2.661621126</v>
-      </c>
-      <c r="E12" s="80">
+        <v>0.14205025342471608</v>
+      </c>
+      <c r="E15" s="76">
         <f t="shared" si="7"/>
-        <v>4.594967228</v>
-      </c>
-      <c r="F12" s="80">
+        <v>0.14205025342471608</v>
+      </c>
+      <c r="F15" s="76">
         <f t="shared" si="7"/>
-        <v>4.798127228</v>
-      </c>
-    </row>
-    <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="75"/>
-      <c r="B13" s="75"/>
-      <c r="C13" s="76"/>
-      <c r="D13" s="75"/>
-      <c r="E13" s="75"/>
-      <c r="F13" s="75"/>
-    </row>
-    <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="75" t="s">
-        <v>359</v>
-      </c>
-      <c r="B14" s="77" t="s">
+        <v>0.14205025342471608</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A16" s="74" t="s">
         <v>360</v>
       </c>
-      <c r="C14" s="77" t="s">
-        <v>360</v>
-      </c>
-      <c r="D14" s="77" t="s">
-        <v>360</v>
-      </c>
-      <c r="E14" s="77" t="s">
+      <c r="B16" s="74" t="s">
         <v>361</v>
       </c>
-      <c r="F14" s="77" t="s">
+      <c r="C16" s="74" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="77" t="s">
-        <v>349</v>
-      </c>
-      <c r="B15" s="77">
-        <f t="shared" ref="B15:F15" si="8">PI()*0.012^2/4*0.04*4*$I$1</f>
-        <v>0.1420502534</v>
-      </c>
-      <c r="C15" s="77">
+      <c r="D16" s="74" t="s">
+        <v>361</v>
+      </c>
+      <c r="E16" s="74" t="s">
+        <v>361</v>
+      </c>
+      <c r="F16" s="74" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A17" s="76" t="s">
+        <v>347</v>
+      </c>
+      <c r="B17" s="74">
+        <f t="shared" ref="B17:F17" si="8">PI()*0.006^2/4*0.03*4*$I$1</f>
+        <v>2.6634422517134264E-2</v>
+      </c>
+      <c r="C17" s="74">
         <f t="shared" si="8"/>
-        <v>0.1420502534</v>
-      </c>
-      <c r="D15" s="77">
+        <v>2.6634422517134264E-2</v>
+      </c>
+      <c r="D17" s="74">
         <f t="shared" si="8"/>
-        <v>0.1420502534</v>
-      </c>
-      <c r="E15" s="77">
+        <v>2.6634422517134264E-2</v>
+      </c>
+      <c r="E17" s="74">
         <f t="shared" si="8"/>
-        <v>0.1420502534</v>
-      </c>
-      <c r="F15" s="77">
+        <v>2.6634422517134264E-2</v>
+      </c>
+      <c r="F17" s="74">
         <f t="shared" si="8"/>
-        <v>0.1420502534</v>
-      </c>
-    </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="75" t="s">
+        <v>2.6634422517134264E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A18" s="74" t="s">
         <v>362</v>
       </c>
-      <c r="B16" s="75" t="s">
+      <c r="B18" s="76" t="s">
         <v>363</v>
       </c>
-      <c r="C16" s="75" t="s">
+      <c r="C18" s="76" t="s">
         <v>363</v>
       </c>
-      <c r="D16" s="75" t="s">
+      <c r="D18" s="76" t="s">
         <v>363</v>
       </c>
-      <c r="E16" s="75" t="s">
+      <c r="E18" s="76" t="s">
         <v>363</v>
       </c>
-      <c r="F16" s="75" t="s">
+      <c r="F18" s="76" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="77" t="s">
-        <v>349</v>
-      </c>
-      <c r="B17" s="75">
-        <f t="shared" ref="B17:F17" si="9">PI()*0.006^2/4*0.03*4*$I$1</f>
-        <v>0.02663442252</v>
-      </c>
-      <c r="C17" s="75">
+    <row r="19" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A19" s="76" t="s">
+        <v>347</v>
+      </c>
+      <c r="B19" s="74">
+        <f t="shared" ref="B19:F19" si="9">0.00575*100</f>
+        <v>0.57499999999999996</v>
+      </c>
+      <c r="C19" s="74">
         <f t="shared" si="9"/>
-        <v>0.02663442252</v>
-      </c>
-      <c r="D17" s="75">
+        <v>0.57499999999999996</v>
+      </c>
+      <c r="D19" s="74">
         <f t="shared" si="9"/>
-        <v>0.02663442252</v>
-      </c>
-      <c r="E17" s="75">
+        <v>0.57499999999999996</v>
+      </c>
+      <c r="E19" s="74">
         <f t="shared" si="9"/>
-        <v>0.02663442252</v>
-      </c>
-      <c r="F17" s="75">
+        <v>0.57499999999999996</v>
+      </c>
+      <c r="F19" s="74">
         <f t="shared" si="9"/>
-        <v>0.02663442252</v>
-      </c>
-    </row>
-    <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="75" t="s">
+        <v>0.57499999999999996</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A20" s="74" t="s">
         <v>364</v>
       </c>
-      <c r="B18" s="77" t="s">
+      <c r="B20" s="76" t="s">
+        <v>363</v>
+      </c>
+      <c r="C20" s="76" t="s">
+        <v>363</v>
+      </c>
+      <c r="D20" s="76" t="s">
+        <v>363</v>
+      </c>
+      <c r="E20" s="76" t="s">
+        <v>363</v>
+      </c>
+      <c r="F20" s="76" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A21" s="76" t="s">
+        <v>347</v>
+      </c>
+      <c r="B21" s="74">
+        <f t="shared" ref="B21:F21" si="10">0.00282*100</f>
+        <v>0.28200000000000003</v>
+      </c>
+      <c r="C21" s="74">
+        <f t="shared" si="10"/>
+        <v>0.28200000000000003</v>
+      </c>
+      <c r="D21" s="74">
+        <f t="shared" si="10"/>
+        <v>0.28200000000000003</v>
+      </c>
+      <c r="E21" s="74">
+        <f t="shared" si="10"/>
+        <v>0.28200000000000003</v>
+      </c>
+      <c r="F21" s="74">
+        <f t="shared" si="10"/>
+        <v>0.28200000000000003</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A22" s="74" t="s">
         <v>365</v>
       </c>
-      <c r="C18" s="77" t="s">
-        <v>365</v>
-      </c>
-      <c r="D18" s="77" t="s">
-        <v>365</v>
-      </c>
-      <c r="E18" s="77" t="s">
-        <v>365</v>
-      </c>
-      <c r="F18" s="77" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="77" t="s">
-        <v>349</v>
-      </c>
-      <c r="B19" s="75">
-        <f t="shared" ref="B19:F19" si="10">0.00575*100</f>
-        <v>0.575</v>
-      </c>
-      <c r="C19" s="75">
-        <f t="shared" si="10"/>
-        <v>0.575</v>
-      </c>
-      <c r="D19" s="75">
-        <f t="shared" si="10"/>
-        <v>0.575</v>
-      </c>
-      <c r="E19" s="75">
-        <f t="shared" si="10"/>
-        <v>0.575</v>
-      </c>
-      <c r="F19" s="75">
-        <f t="shared" si="10"/>
-        <v>0.575</v>
-      </c>
-    </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="75" t="s">
+      <c r="B22" s="95" t="s">
         <v>366</v>
       </c>
-      <c r="B20" s="77" t="s">
-        <v>365</v>
-      </c>
-      <c r="C20" s="77" t="s">
-        <v>365</v>
-      </c>
-      <c r="D20" s="77" t="s">
-        <v>365</v>
-      </c>
-      <c r="E20" s="77" t="s">
-        <v>365</v>
-      </c>
-      <c r="F20" s="77" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="77" t="s">
-        <v>349</v>
-      </c>
-      <c r="B21" s="75">
-        <f t="shared" ref="B21:F21" si="11">0.00282*100</f>
-        <v>0.282</v>
-      </c>
-      <c r="C21" s="75">
+      <c r="C22" s="96"/>
+      <c r="D22" s="96"/>
+      <c r="E22" s="96"/>
+      <c r="F22" s="97"/>
+    </row>
+    <row r="23" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A23" s="76" t="s">
+        <v>347</v>
+      </c>
+      <c r="B23" s="74">
+        <f t="shared" ref="B23:F23" si="11">PI()*(0.012^2/4+0.01^2/4)*$I$1</f>
+        <v>1.5043516421714724</v>
+      </c>
+      <c r="C23" s="74">
         <f t="shared" si="11"/>
-        <v>0.282</v>
-      </c>
-      <c r="D21" s="75">
+        <v>1.5043516421714724</v>
+      </c>
+      <c r="D23" s="74">
         <f t="shared" si="11"/>
-        <v>0.282</v>
-      </c>
-      <c r="E21" s="75">
+        <v>1.5043516421714724</v>
+      </c>
+      <c r="E23" s="74">
         <f t="shared" si="11"/>
-        <v>0.282</v>
-      </c>
-      <c r="F21" s="75">
+        <v>1.5043516421714724</v>
+      </c>
+      <c r="F23" s="74">
         <f t="shared" si="11"/>
-        <v>0.282</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="75" t="s">
+        <v>1.5043516421714724</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A24" s="74" t="s">
         <v>367</v>
       </c>
-      <c r="B22" s="81" t="s">
+      <c r="B24" s="74" t="s">
         <v>368</v>
       </c>
-      <c r="F22" s="82"/>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="77" t="s">
-        <v>349</v>
-      </c>
-      <c r="B23" s="75">
-        <f t="shared" ref="B23:F23" si="12">PI()*(0.012^2/4+0.01^2/4)*$I$1</f>
-        <v>1.504351642</v>
-      </c>
-      <c r="C23" s="75">
+      <c r="C24" s="74" t="s">
+        <v>368</v>
+      </c>
+      <c r="D24" s="74" t="s">
+        <v>368</v>
+      </c>
+      <c r="E24" s="74" t="s">
+        <v>369</v>
+      </c>
+      <c r="F24" s="74" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A25" s="76" t="s">
+        <v>347</v>
+      </c>
+      <c r="B25" s="74">
+        <f t="shared" ref="B25:D25" si="12">0.0116*10</f>
+        <v>0.11599999999999999</v>
+      </c>
+      <c r="C25" s="74">
         <f t="shared" si="12"/>
-        <v>1.504351642</v>
-      </c>
-      <c r="D23" s="75">
+        <v>0.11599999999999999</v>
+      </c>
+      <c r="D25" s="74">
         <f t="shared" si="12"/>
-        <v>1.504351642</v>
-      </c>
-      <c r="E23" s="75">
-        <f t="shared" si="12"/>
-        <v>1.504351642</v>
-      </c>
-      <c r="F23" s="75">
-        <f t="shared" si="12"/>
-        <v>1.504351642</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="75" t="s">
-        <v>369</v>
-      </c>
-      <c r="B24" s="75" t="s">
+        <v>0.11599999999999999</v>
+      </c>
+      <c r="E25" s="74">
+        <f t="shared" ref="E25:F25" si="13">0.0116*10+3*0.0173</f>
+        <v>0.16789999999999999</v>
+      </c>
+      <c r="F25" s="74">
+        <f t="shared" si="13"/>
+        <v>0.16789999999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A26" s="74" t="s">
         <v>370</v>
       </c>
-      <c r="C24" s="75" t="s">
-        <v>370</v>
-      </c>
-      <c r="D24" s="75" t="s">
-        <v>370</v>
-      </c>
-      <c r="E24" s="75" t="s">
+      <c r="B26" s="74" t="s">
         <v>371</v>
       </c>
-      <c r="F24" s="75" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="77" t="s">
-        <v>349</v>
-      </c>
-      <c r="B25" s="75">
-        <f t="shared" ref="B25:D25" si="13">0.0116*10</f>
-        <v>0.116</v>
-      </c>
-      <c r="C25" s="75">
-        <f t="shared" si="13"/>
-        <v>0.116</v>
-      </c>
-      <c r="D25" s="75">
-        <f t="shared" si="13"/>
-        <v>0.116</v>
-      </c>
-      <c r="E25" s="75">
-        <f t="shared" ref="E25:F25" si="14">0.0116*10+3*0.0173</f>
-        <v>0.1679</v>
-      </c>
-      <c r="F25" s="75">
+      <c r="C26" s="74"/>
+      <c r="D26" s="74"/>
+      <c r="E26" s="74"/>
+      <c r="F26" s="74"/>
+    </row>
+    <row r="27" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A27" s="76" t="s">
+        <v>347</v>
+      </c>
+      <c r="B27" s="80">
+        <f t="shared" ref="B27:F27" si="14">2/100</f>
+        <v>0.02</v>
+      </c>
+      <c r="C27" s="80">
         <f t="shared" si="14"/>
-        <v>0.1679</v>
-      </c>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="75" t="s">
+        <v>0.02</v>
+      </c>
+      <c r="D27" s="80">
+        <f t="shared" si="14"/>
+        <v>0.02</v>
+      </c>
+      <c r="E27" s="80">
+        <f t="shared" si="14"/>
+        <v>0.02</v>
+      </c>
+      <c r="F27" s="80">
+        <f t="shared" si="14"/>
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A28" s="81" t="s">
         <v>372</v>
       </c>
-      <c r="B26" s="75" t="s">
-        <v>373</v>
-      </c>
-      <c r="C26" s="75"/>
-      <c r="D26" s="75"/>
-      <c r="E26" s="75"/>
-      <c r="F26" s="75"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="77" t="s">
-        <v>349</v>
-      </c>
-      <c r="B27" s="83">
-        <f t="shared" ref="B27:F27" si="15">2/100</f>
-        <v>0.02</v>
-      </c>
-      <c r="C27" s="83">
+      <c r="B28" s="82">
+        <f t="shared" ref="B28:F28" si="15">SUM(B15,B17,B19,B21,B23,B25,B27)</f>
+        <v>2.6660363181133229</v>
+      </c>
+      <c r="C28" s="82">
         <f t="shared" si="15"/>
-        <v>0.02</v>
-      </c>
-      <c r="D27" s="83">
+        <v>2.6660363181133229</v>
+      </c>
+      <c r="D28" s="82">
         <f t="shared" si="15"/>
-        <v>0.02</v>
-      </c>
-      <c r="E27" s="83">
+        <v>2.6660363181133229</v>
+      </c>
+      <c r="E28" s="82">
         <f t="shared" si="15"/>
-        <v>0.02</v>
-      </c>
-      <c r="F27" s="83">
+        <v>2.7179363181133227</v>
+      </c>
+      <c r="F28" s="82">
         <f t="shared" si="15"/>
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="84" t="s">
-        <v>374</v>
-      </c>
-      <c r="B28" s="85">
-        <f t="shared" ref="B28:F28" si="16">SUM(B15,B17,B19,B21,B23,B25,B27)</f>
-        <v>2.666036318</v>
-      </c>
-      <c r="C28" s="85">
-        <f t="shared" si="16"/>
-        <v>2.666036318</v>
-      </c>
-      <c r="D28" s="85">
-        <f t="shared" si="16"/>
-        <v>2.666036318</v>
-      </c>
-      <c r="E28" s="85">
-        <f t="shared" si="16"/>
-        <v>2.717936318</v>
-      </c>
-      <c r="F28" s="85">
-        <f t="shared" si="16"/>
-        <v>2.717936318</v>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="B29" s="86"/>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="87"/>
-      <c r="B30" s="88" t="s">
-        <v>358</v>
-      </c>
-      <c r="C30" s="89" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="90" t="s">
+        <v>2.7179363181133227</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15.75" customHeight="1">
+      <c r="B29" s="83"/>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A30" s="84"/>
+      <c r="B30" s="85" t="s">
+        <v>356</v>
+      </c>
+      <c r="C30" s="86" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A31" s="87" t="s">
+        <v>338</v>
+      </c>
+      <c r="B31" s="88">
+        <v>2.4803611258567138</v>
+      </c>
+      <c r="C31" s="89">
+        <v>2.6660363181133229</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A32" s="87" t="s">
+        <v>339</v>
+      </c>
+      <c r="B32" s="90">
+        <v>2.5926211258567138</v>
+      </c>
+      <c r="C32" s="90">
+        <v>2.6660363181133229</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A33" s="87" t="s">
         <v>340</v>
       </c>
-      <c r="B31" s="91">
-        <v>2.4803611258567138</v>
-      </c>
-      <c r="C31" s="92">
-        <v>2.666036318113323</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="90" t="s">
+      <c r="B33" s="90">
+        <v>2.6616211258567137</v>
+      </c>
+      <c r="C33" s="90">
+        <v>2.6660363181133229</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A34" s="87" t="s">
         <v>341</v>
       </c>
-      <c r="B32" s="93">
-        <v>2.592621125856714</v>
-      </c>
-      <c r="C32" s="93">
-        <v>2.666036318113323</v>
-      </c>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="90" t="s">
+      <c r="B34" s="90">
+        <v>4.5949672284066292</v>
+      </c>
+      <c r="C34" s="90">
+        <v>2.7179363181133227</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A35" s="87" t="s">
         <v>342</v>
       </c>
-      <c r="B33" s="93">
-        <v>2.6616211258567137</v>
-      </c>
-      <c r="C33" s="93">
-        <v>2.666036318113323</v>
-      </c>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="90" t="s">
-        <v>343</v>
-      </c>
-      <c r="B34" s="93">
-        <v>4.594967228406629</v>
-      </c>
-      <c r="C34" s="93">
+      <c r="B35" s="91">
+        <v>4.7981272284066288</v>
+      </c>
+      <c r="C35" s="91">
         <v>2.7179363181133227</v>
       </c>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="90" t="s">
-        <v>344</v>
-      </c>
-      <c r="B35" s="94">
-        <v>4.798127228406629</v>
-      </c>
-      <c r="C35" s="94">
-        <v>2.7179363181133227</v>
-      </c>
-    </row>
-    <row r="36" ht="15.75" customHeight="1"/>
-    <row r="37" ht="15.75" customHeight="1"/>
-    <row r="38" ht="15.75" customHeight="1"/>
-    <row r="39" ht="15.75" customHeight="1"/>
-    <row r="40" ht="15.75" customHeight="1"/>
-    <row r="41" ht="15.75" customHeight="1"/>
-    <row r="42" ht="15.75" customHeight="1"/>
-    <row r="43" ht="15.75" customHeight="1"/>
-    <row r="44" ht="15.75" customHeight="1"/>
-    <row r="45" ht="15.75" customHeight="1"/>
-    <row r="46" ht="15.75" customHeight="1"/>
-    <row r="47" ht="15.75" customHeight="1"/>
-    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="36" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="37" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="38" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="39" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="40" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="41" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="42" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="43" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="44" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="45" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="46" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="47" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="48" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>
@@ -10211,7 +11359,7 @@
   <mergeCells count="1">
     <mergeCell ref="B22:F22"/>
   </mergeCells>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>